--- a/villa_finance.xlsx
+++ b/villa_finance.xlsx
@@ -1177,7 +1177,7 @@
     <row r="38">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Вопросов финдиректору</t>
+          <t>Открытых вопросов</t>
         </is>
       </c>
       <c r="C38" s="12">
@@ -7593,7 +7593,7 @@
     <row r="65">
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>5. Вопросы финансовому директору</t>
+          <t>5. Вопросы</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr"/>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="G95" s="22" t="inlineStr">
         <is>
-          <t>Вопрос финдиректору (допущение в расчёте)</t>
+          <t>Вопрос (допущение в расчёте)</t>
         </is>
       </c>
       <c r="H95" s="19" t="inlineStr">
         <is>
-          <t>OTA fee по отмене считаю сторнированной: fee × (gross − refund) / gross = 0. Вопрос финдиректору: удерживает ли OTA комиссию</t>
+          <t>OTA fee по отмене считаю сторнированной: fee × (gross − refund) / gross = 0. Вопрос: удерживает ли OTA комиссию</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="G96" s="22" t="inlineStr">
         <is>
-          <t>Вопрос финдиректору (в расчёте как есть)</t>
+          <t>Вопрос (в расчёте как есть)</t>
         </is>
       </c>
       <c r="H96" s="19" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="G108" s="22" t="inlineStr">
         <is>
-          <t>Вопрос финдиректору (в расчёте)</t>
+          <t>Вопрос (в расчёте)</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="G109" s="22" t="inlineStr">
         <is>
-          <t>Вопрос финдиректору</t>
+          <t>Вопрос</t>
         </is>
       </c>
       <c r="H109" s="19" t="inlineStr">

--- a/villa_finance.xlsx
+++ b/villa_finance.xlsx
@@ -919,11 +919,11 @@
       </c>
       <c r="C18" s="12">
         <f>IF($C$4="Все",SUM(calc_reservations!$AN$2:$AN$152),SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,$C$4))</f>
-        <v>748</v>
+        <v>685</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>включая ночи, проданные дважды (пересечения); при 20 виллах × 61 день доступно 1 220 ночей, загрузку по этой строке считать нельзя</t>
+          <t>без отменённых броней, но включая ночи, проданные дважды (пересечения); при 20 виллах × 61 день доступно 1 220 ночей, загрузку по этой строке считать нельзя</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L43" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$3)</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M43" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$3)</f>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="L45" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$5)</f>
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M45" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$5)</f>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L47" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$7)</f>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="M47" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$7)</f>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="L48" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$8)</f>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M48" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$8)</f>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="L53" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$13)</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M53" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$13)</f>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="L54" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$14)</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M54" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$14)</f>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="L56" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$16)</f>
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M56" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$16)</f>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="L57" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$17)</f>
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M57" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$17)</f>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="L61" s="12">
         <f>SUMIFS(calc_reservations!$AN$2:$AN$152,calc_reservations!$B$2:$B$152,properties!$A$21)</f>
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M61" s="12">
         <f>SUMIFS(calc_reservations!$AO$2:$AO$152,calc_reservations!$B$2:$B$152,properties!$A$21)</f>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="L62" s="14">
         <f>SUM(L42:L61)</f>
-        <v>748</v>
+        <v>685</v>
       </c>
       <c r="M62" s="14">
         <f>SUM(M42:M61)</f>
@@ -6839,15 +6839,15 @@
       </c>
       <c r="C15" s="31">
         <f>IF(Dashboard!$C$4="Все",SUM(calc_reservations!$AX$2:$AX$152),SUMIFS(calc_reservations!$AX$2:$AX$152,calc_reservations!$B$2:$B$152,Dashboard!$C$4))</f>
-        <v>748</v>
+        <v>685</v>
       </c>
       <c r="D15" s="31">
         <f>IF(Dashboard!$C$4="Все",SUM(calc_reservations!$BD$2:$BD$152),SUMIFS(calc_reservations!$BD$2:$BD$152,calc_reservations!$B$2:$B$152,Dashboard!$C$4))</f>
-        <v>515</v>
+        <v>452</v>
       </c>
       <c r="E15" s="31">
         <f>IF(Dashboard!$C$4="Все",SUM(calc_reservations!$BJ$2:$BJ$152),SUMIFS(calc_reservations!$BJ$2:$BJ$152,calc_reservations!$B$2:$B$152,Dashboard!$C$4))</f>
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="F15" s="31">
         <f>C15-E15</f>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AN1" s="13" t="inlineStr">
         <is>
-          <t>ночей · период (в расчёте)</t>
+          <t>ночей · период (в расчёте, без отмен)</t>
         </is>
       </c>
       <c r="AO1" s="13" t="inlineStr">
@@ -12608,7 +12608,7 @@
         <v>0</v>
       </c>
       <c r="AN2" s="9">
-        <f>AD2*T2</f>
+        <f>IF(E2="cancelled",0,AD2*T2)</f>
         <v>3</v>
       </c>
       <c r="AO2" s="9">
@@ -12648,7 +12648,7 @@
         <v>898557.6100000001</v>
       </c>
       <c r="AX2" s="31">
-        <f>AD2*AP2</f>
+        <f>IF(E2="cancelled",0,AD2*AP2)</f>
         <v>3</v>
       </c>
       <c r="AY2" s="31">
@@ -12672,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="BD2" s="31">
-        <f>AD2*AQ2</f>
+        <f>IF(E2="cancelled",0,AD2*AQ2)</f>
         <v>0</v>
       </c>
       <c r="BE2" s="31">
@@ -12696,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="BJ2" s="31">
-        <f>AD2*AR2</f>
+        <f>IF(E2="cancelled",0,AD2*AR2)</f>
         <v>0</v>
       </c>
       <c r="BK2" s="31">
@@ -12870,7 +12870,7 @@
         <v>10011978</v>
       </c>
       <c r="AN3" s="9">
-        <f>AD3*T3</f>
+        <f>IF(E3="cancelled",0,AD3*T3)</f>
         <v>4</v>
       </c>
       <c r="AO3" s="9">
@@ -12910,7 +12910,7 @@
         <v>2002395.6600000001</v>
       </c>
       <c r="AX3" s="31">
-        <f>AD3*AP3</f>
+        <f>IF(E3="cancelled",0,AD3*AP3)</f>
         <v>4</v>
       </c>
       <c r="AY3" s="31">
@@ -12934,7 +12934,7 @@
         <v>2002395.6600000001</v>
       </c>
       <c r="BD3" s="31">
-        <f>AD3*AQ3</f>
+        <f>IF(E3="cancelled",0,AD3*AQ3)</f>
         <v>4</v>
       </c>
       <c r="BE3" s="31">
@@ -12958,7 +12958,7 @@
         <v>0</v>
       </c>
       <c r="BJ3" s="31">
-        <f>AD3*AR3</f>
+        <f>IF(E3="cancelled",0,AD3*AR3)</f>
         <v>0</v>
       </c>
       <c r="BK3" s="31">
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AN4" s="9">
-        <f>AD4*T4</f>
+        <f>IF(E4="cancelled",0,AD4*T4)</f>
         <v>7</v>
       </c>
       <c r="AO4" s="9">
@@ -13172,7 +13172,7 @@
         <v>2069045.5200000003</v>
       </c>
       <c r="AX4" s="31">
-        <f>AD4*AP4</f>
+        <f>IF(E4="cancelled",0,AD4*AP4)</f>
         <v>7</v>
       </c>
       <c r="AY4" s="31">
@@ -13196,7 +13196,7 @@
         <v>2069045.5200000003</v>
       </c>
       <c r="BD4" s="31">
-        <f>AD4*AQ4</f>
+        <f>IF(E4="cancelled",0,AD4*AQ4)</f>
         <v>7</v>
       </c>
       <c r="BE4" s="31">
@@ -13220,7 +13220,7 @@
         <v>2069045.5200000003</v>
       </c>
       <c r="BJ4" s="31">
-        <f>AD4*AR4</f>
+        <f>IF(E4="cancelled",0,AD4*AR4)</f>
         <v>7</v>
       </c>
       <c r="BK4" s="31">
@@ -13394,7 +13394,7 @@
         <v>2386450</v>
       </c>
       <c r="AN5" s="9">
-        <f>AD5*T5</f>
+        <f>IF(E5="cancelled",0,AD5*T5)</f>
         <v>8</v>
       </c>
       <c r="AO5" s="9">
@@ -13434,7 +13434,7 @@
         <v>561517.6</v>
       </c>
       <c r="AX5" s="31">
-        <f>AD5*AP5</f>
+        <f>IF(E5="cancelled",0,AD5*AP5)</f>
         <v>8</v>
       </c>
       <c r="AY5" s="31">
@@ -13458,7 +13458,7 @@
         <v>561517.6</v>
       </c>
       <c r="BD5" s="31">
-        <f>AD5*AQ5</f>
+        <f>IF(E5="cancelled",0,AD5*AQ5)</f>
         <v>8</v>
       </c>
       <c r="BE5" s="31">
@@ -13482,7 +13482,7 @@
         <v>561517.6</v>
       </c>
       <c r="BJ5" s="31">
-        <f>AD5*AR5</f>
+        <f>IF(E5="cancelled",0,AD5*AR5)</f>
         <v>8</v>
       </c>
       <c r="BK5" s="31">
@@ -13656,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="AN6" s="9">
-        <f>AD6*T6</f>
+        <f>IF(E6="cancelled",0,AD6*T6)</f>
         <v>7</v>
       </c>
       <c r="AO6" s="9">
@@ -13696,7 +13696,7 @@
         <v>1334497.9600000002</v>
       </c>
       <c r="AX6" s="31">
-        <f>AD6*AP6</f>
+        <f>IF(E6="cancelled",0,AD6*AP6)</f>
         <v>7</v>
       </c>
       <c r="AY6" s="31">
@@ -13720,7 +13720,7 @@
         <v>0</v>
       </c>
       <c r="BD6" s="31">
-        <f>AD6*AQ6</f>
+        <f>IF(E6="cancelled",0,AD6*AQ6)</f>
         <v>0</v>
       </c>
       <c r="BE6" s="31">
@@ -13744,7 +13744,7 @@
         <v>0</v>
       </c>
       <c r="BJ6" s="31">
-        <f>AD6*AR6</f>
+        <f>IF(E6="cancelled",0,AD6*AR6)</f>
         <v>0</v>
       </c>
       <c r="BK6" s="31">
@@ -13918,7 +13918,7 @@
         <v>10719326</v>
       </c>
       <c r="AN7" s="9">
-        <f>AD7*T7</f>
+        <f>IF(E7="cancelled",0,AD7*T7)</f>
         <v>7</v>
       </c>
       <c r="AO7" s="9">
@@ -13958,7 +13958,7 @@
         <v>2195524.5</v>
       </c>
       <c r="AX7" s="31">
-        <f>AD7*AP7</f>
+        <f>IF(E7="cancelled",0,AD7*AP7)</f>
         <v>7</v>
       </c>
       <c r="AY7" s="31">
@@ -13982,7 +13982,7 @@
         <v>2195524.5</v>
       </c>
       <c r="BD7" s="31">
-        <f>AD7*AQ7</f>
+        <f>IF(E7="cancelled",0,AD7*AQ7)</f>
         <v>7</v>
       </c>
       <c r="BE7" s="31">
@@ -14006,7 +14006,7 @@
         <v>2195524.5</v>
       </c>
       <c r="BJ7" s="31">
-        <f>AD7*AR7</f>
+        <f>IF(E7="cancelled",0,AD7*AR7)</f>
         <v>7</v>
       </c>
       <c r="BK7" s="31">
@@ -14180,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="AN8" s="9">
-        <f>AD8*T8</f>
+        <f>IF(E8="cancelled",0,AD8*T8)</f>
         <v>8</v>
       </c>
       <c r="AO8" s="9">
@@ -14220,7 +14220,7 @@
         <v>2101353.5100000002</v>
       </c>
       <c r="AX8" s="31">
-        <f>AD8*AP8</f>
+        <f>IF(E8="cancelled",0,AD8*AP8)</f>
         <v>8</v>
       </c>
       <c r="AY8" s="31">
@@ -14244,7 +14244,7 @@
         <v>0</v>
       </c>
       <c r="BD8" s="31">
-        <f>AD8*AQ8</f>
+        <f>IF(E8="cancelled",0,AD8*AQ8)</f>
         <v>0</v>
       </c>
       <c r="BE8" s="31">
@@ -14268,7 +14268,7 @@
         <v>0</v>
       </c>
       <c r="BJ8" s="31">
-        <f>AD8*AR8</f>
+        <f>IF(E8="cancelled",0,AD8*AR8)</f>
         <v>0</v>
       </c>
       <c r="BK8" s="31">
@@ -14442,7 +14442,7 @@
         <v>13048995</v>
       </c>
       <c r="AN9" s="9">
-        <f>AD9*T9</f>
+        <f>IF(E9="cancelled",0,AD9*T9)</f>
         <v>4</v>
       </c>
       <c r="AO9" s="9">
@@ -14482,7 +14482,7 @@
         <v>2520828.5100000002</v>
       </c>
       <c r="AX9" s="31">
-        <f>AD9*AP9</f>
+        <f>IF(E9="cancelled",0,AD9*AP9)</f>
         <v>4</v>
       </c>
       <c r="AY9" s="31">
@@ -14506,7 +14506,7 @@
         <v>2520828.5100000002</v>
       </c>
       <c r="BD9" s="31">
-        <f>AD9*AQ9</f>
+        <f>IF(E9="cancelled",0,AD9*AQ9)</f>
         <v>4</v>
       </c>
       <c r="BE9" s="31">
@@ -14530,7 +14530,7 @@
         <v>0</v>
       </c>
       <c r="BJ9" s="31">
-        <f>AD9*AR9</f>
+        <f>IF(E9="cancelled",0,AD9*AR9)</f>
         <v>0</v>
       </c>
       <c r="BK9" s="31">
@@ -14704,7 +14704,7 @@
         <v>0</v>
       </c>
       <c r="AN10" s="9">
-        <f>AD10*T10</f>
+        <f>IF(E10="cancelled",0,AD10*T10)</f>
         <v>4</v>
       </c>
       <c r="AO10" s="9">
@@ -14744,7 +14744,7 @@
         <v>2513726.7600000002</v>
       </c>
       <c r="AX10" s="31">
-        <f>AD10*AP10</f>
+        <f>IF(E10="cancelled",0,AD10*AP10)</f>
         <v>4</v>
       </c>
       <c r="AY10" s="31">
@@ -14768,7 +14768,7 @@
         <v>2513726.7600000002</v>
       </c>
       <c r="BD10" s="31">
-        <f>AD10*AQ10</f>
+        <f>IF(E10="cancelled",0,AD10*AQ10)</f>
         <v>4</v>
       </c>
       <c r="BE10" s="31">
@@ -14792,7 +14792,7 @@
         <v>2513726.7600000002</v>
       </c>
       <c r="BJ10" s="31">
-        <f>AD10*AR10</f>
+        <f>IF(E10="cancelled",0,AD10*AR10)</f>
         <v>4</v>
       </c>
       <c r="BK10" s="31">
@@ -14966,7 +14966,7 @@
         <v>2473691</v>
       </c>
       <c r="AN11" s="9">
-        <f>AD11*T11</f>
+        <f>IF(E11="cancelled",0,AD11*T11)</f>
         <v>7</v>
       </c>
       <c r="AO11" s="9">
@@ -15006,7 +15006,7 @@
         <v>477872.04000000004</v>
       </c>
       <c r="AX11" s="31">
-        <f>AD11*AP11</f>
+        <f>IF(E11="cancelled",0,AD11*AP11)</f>
         <v>7</v>
       </c>
       <c r="AY11" s="31">
@@ -15030,7 +15030,7 @@
         <v>477872.04000000004</v>
       </c>
       <c r="BD11" s="31">
-        <f>AD11*AQ11</f>
+        <f>IF(E11="cancelled",0,AD11*AQ11)</f>
         <v>7</v>
       </c>
       <c r="BE11" s="31">
@@ -15054,7 +15054,7 @@
         <v>0</v>
       </c>
       <c r="BJ11" s="31">
-        <f>AD11*AR11</f>
+        <f>IF(E11="cancelled",0,AD11*AR11)</f>
         <v>0</v>
       </c>
       <c r="BK11" s="31">
@@ -15228,7 +15228,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="9">
-        <f>AD12*T12</f>
+        <f>IF(E12="cancelled",0,AD12*T12)</f>
         <v>7</v>
       </c>
       <c r="AO12" s="9">
@@ -15268,7 +15268,7 @@
         <v>1096405.6</v>
       </c>
       <c r="AX12" s="31">
-        <f>AD12*AP12</f>
+        <f>IF(E12="cancelled",0,AD12*AP12)</f>
         <v>7</v>
       </c>
       <c r="AY12" s="31">
@@ -15292,7 +15292,7 @@
         <v>0</v>
       </c>
       <c r="BD12" s="31">
-        <f>AD12*AQ12</f>
+        <f>IF(E12="cancelled",0,AD12*AQ12)</f>
         <v>0</v>
       </c>
       <c r="BE12" s="31">
@@ -15316,7 +15316,7 @@
         <v>0</v>
       </c>
       <c r="BJ12" s="31">
-        <f>AD12*AR12</f>
+        <f>IF(E12="cancelled",0,AD12*AR12)</f>
         <v>0</v>
       </c>
       <c r="BK12" s="31">
@@ -15490,7 +15490,7 @@
         <v>11352171</v>
       </c>
       <c r="AN13" s="9">
-        <f>AD13*T13</f>
+        <f>IF(E13="cancelled",0,AD13*T13)</f>
         <v>3</v>
       </c>
       <c r="AO13" s="9">
@@ -15530,7 +15530,7 @@
         <v>2193032.98</v>
       </c>
       <c r="AX13" s="31">
-        <f>AD13*AP13</f>
+        <f>IF(E13="cancelled",0,AD13*AP13)</f>
         <v>3</v>
       </c>
       <c r="AY13" s="31">
@@ -15554,7 +15554,7 @@
         <v>2193032.98</v>
       </c>
       <c r="BD13" s="31">
-        <f>AD13*AQ13</f>
+        <f>IF(E13="cancelled",0,AD13*AQ13)</f>
         <v>3</v>
       </c>
       <c r="BE13" s="31">
@@ -15578,7 +15578,7 @@
         <v>0</v>
       </c>
       <c r="BJ13" s="31">
-        <f>AD13*AR13</f>
+        <f>IF(E13="cancelled",0,AD13*AR13)</f>
         <v>0</v>
       </c>
       <c r="BK13" s="31">
@@ -15752,7 +15752,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="9">
-        <f>AD14*T14</f>
+        <f>IF(E14="cancelled",0,AD14*T14)</f>
         <v>3</v>
       </c>
       <c r="AO14" s="9">
@@ -15792,7 +15792,7 @@
         <v>1959271.8</v>
       </c>
       <c r="AX14" s="31">
-        <f>AD14*AP14</f>
+        <f>IF(E14="cancelled",0,AD14*AP14)</f>
         <v>3</v>
       </c>
       <c r="AY14" s="31">
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="BD14" s="31">
-        <f>AD14*AQ14</f>
+        <f>IF(E14="cancelled",0,AD14*AQ14)</f>
         <v>0</v>
       </c>
       <c r="BE14" s="31">
@@ -15840,7 +15840,7 @@
         <v>0</v>
       </c>
       <c r="BJ14" s="31">
-        <f>AD14*AR14</f>
+        <f>IF(E14="cancelled",0,AD14*AR14)</f>
         <v>0</v>
       </c>
       <c r="BK14" s="31">
@@ -16014,7 +16014,7 @@
         <v>3560967</v>
       </c>
       <c r="AN15" s="9">
-        <f>AD15*T15</f>
+        <f>IF(E15="cancelled",0,AD15*T15)</f>
         <v>3</v>
       </c>
       <c r="AO15" s="9">
@@ -16054,7 +16054,7 @@
         <v>729354.7400000001</v>
       </c>
       <c r="AX15" s="31">
-        <f>AD15*AP15</f>
+        <f>IF(E15="cancelled",0,AD15*AP15)</f>
         <v>3</v>
       </c>
       <c r="AY15" s="31">
@@ -16078,7 +16078,7 @@
         <v>729354.7400000001</v>
       </c>
       <c r="BD15" s="31">
-        <f>AD15*AQ15</f>
+        <f>IF(E15="cancelled",0,AD15*AQ15)</f>
         <v>3</v>
       </c>
       <c r="BE15" s="31">
@@ -16102,7 +16102,7 @@
         <v>729354.7400000001</v>
       </c>
       <c r="BJ15" s="31">
-        <f>AD15*AR15</f>
+        <f>IF(E15="cancelled",0,AD15*AR15)</f>
         <v>3</v>
       </c>
       <c r="BK15" s="31">
@@ -16276,7 +16276,7 @@
         <v>0</v>
       </c>
       <c r="AN16" s="9">
-        <f>AD16*T16</f>
+        <f>IF(E16="cancelled",0,AD16*T16)</f>
         <v>2</v>
       </c>
       <c r="AO16" s="9">
@@ -16316,7 +16316,7 @@
         <v>2316928.98</v>
       </c>
       <c r="AX16" s="31">
-        <f>AD16*AP16</f>
+        <f>IF(E16="cancelled",0,AD16*AP16)</f>
         <v>2</v>
       </c>
       <c r="AY16" s="31">
@@ -16340,7 +16340,7 @@
         <v>2316928.98</v>
       </c>
       <c r="BD16" s="31">
-        <f>AD16*AQ16</f>
+        <f>IF(E16="cancelled",0,AD16*AQ16)</f>
         <v>2</v>
       </c>
       <c r="BE16" s="31">
@@ -16364,7 +16364,7 @@
         <v>2316928.98</v>
       </c>
       <c r="BJ16" s="31">
-        <f>AD16*AR16</f>
+        <f>IF(E16="cancelled",0,AD16*AR16)</f>
         <v>2</v>
       </c>
       <c r="BK16" s="31">
@@ -16538,7 +16538,7 @@
         <v>5601662</v>
       </c>
       <c r="AN17" s="9">
-        <f>AD17*T17</f>
+        <f>IF(E17="cancelled",0,AD17*T17)</f>
         <v>5</v>
       </c>
       <c r="AO17" s="9">
@@ -16578,7 +16578,7 @@
         <v>1273105</v>
       </c>
       <c r="AX17" s="31">
-        <f>AD17*AP17</f>
+        <f>IF(E17="cancelled",0,AD17*AP17)</f>
         <v>5</v>
       </c>
       <c r="AY17" s="31">
@@ -16602,7 +16602,7 @@
         <v>1273105</v>
       </c>
       <c r="BD17" s="31">
-        <f>AD17*AQ17</f>
+        <f>IF(E17="cancelled",0,AD17*AQ17)</f>
         <v>5</v>
       </c>
       <c r="BE17" s="31">
@@ -16626,7 +16626,7 @@
         <v>1273105</v>
       </c>
       <c r="BJ17" s="31">
-        <f>AD17*AR17</f>
+        <f>IF(E17="cancelled",0,AD17*AR17)</f>
         <v>5</v>
       </c>
       <c r="BK17" s="31">
@@ -16800,7 +16800,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="9">
-        <f>AD18*T18</f>
+        <f>IF(E18="cancelled",0,AD18*T18)</f>
         <v>2</v>
       </c>
       <c r="AO18" s="9">
@@ -16840,7 +16840,7 @@
         <v>1732463.8800000001</v>
       </c>
       <c r="AX18" s="31">
-        <f>AD18*AP18</f>
+        <f>IF(E18="cancelled",0,AD18*AP18)</f>
         <v>2</v>
       </c>
       <c r="AY18" s="31">
@@ -16864,7 +16864,7 @@
         <v>0</v>
       </c>
       <c r="BD18" s="31">
-        <f>AD18*AQ18</f>
+        <f>IF(E18="cancelled",0,AD18*AQ18)</f>
         <v>0</v>
       </c>
       <c r="BE18" s="31">
@@ -16888,7 +16888,7 @@
         <v>0</v>
       </c>
       <c r="BJ18" s="31">
-        <f>AD18*AR18</f>
+        <f>IF(E18="cancelled",0,AD18*AR18)</f>
         <v>0</v>
       </c>
       <c r="BK18" s="31">
@@ -17062,7 +17062,7 @@
         <v>12741209</v>
       </c>
       <c r="AN19" s="9">
-        <f>AD19*T19</f>
+        <f>IF(E19="cancelled",0,AD19*T19)</f>
         <v>6</v>
       </c>
       <c r="AO19" s="9">
@@ -17102,7 +17102,7 @@
         <v>2548241.8600000003</v>
       </c>
       <c r="AX19" s="31">
-        <f>AD19*AP19</f>
+        <f>IF(E19="cancelled",0,AD19*AP19)</f>
         <v>6</v>
       </c>
       <c r="AY19" s="31">
@@ -17126,7 +17126,7 @@
         <v>2548241.8600000003</v>
       </c>
       <c r="BD19" s="31">
-        <f>AD19*AQ19</f>
+        <f>IF(E19="cancelled",0,AD19*AQ19)</f>
         <v>6</v>
       </c>
       <c r="BE19" s="31">
@@ -17150,7 +17150,7 @@
         <v>0</v>
       </c>
       <c r="BJ19" s="31">
-        <f>AD19*AR19</f>
+        <f>IF(E19="cancelled",0,AD19*AR19)</f>
         <v>0</v>
       </c>
       <c r="BK19" s="31">
@@ -17324,7 +17324,7 @@
         <v>0</v>
       </c>
       <c r="AN20" s="9">
-        <f>AD20*T20</f>
+        <f>IF(E20="cancelled",0,AD20*T20)</f>
         <v>2</v>
       </c>
       <c r="AO20" s="9">
@@ -17364,7 +17364,7 @@
         <v>2293481.39</v>
       </c>
       <c r="AX20" s="31">
-        <f>AD20*AP20</f>
+        <f>IF(E20="cancelled",0,AD20*AP20)</f>
         <v>2</v>
       </c>
       <c r="AY20" s="31">
@@ -17388,7 +17388,7 @@
         <v>0</v>
       </c>
       <c r="BD20" s="31">
-        <f>AD20*AQ20</f>
+        <f>IF(E20="cancelled",0,AD20*AQ20)</f>
         <v>0</v>
       </c>
       <c r="BE20" s="31">
@@ -17412,7 +17412,7 @@
         <v>0</v>
       </c>
       <c r="BJ20" s="31">
-        <f>AD20*AR20</f>
+        <f>IF(E20="cancelled",0,AD20*AR20)</f>
         <v>0</v>
       </c>
       <c r="BK20" s="31">
@@ -17586,7 +17586,7 @@
         <v>2990297</v>
       </c>
       <c r="AN21" s="9">
-        <f>AD21*T21</f>
+        <f>IF(E21="cancelled",0,AD21*T21)</f>
         <v>3</v>
       </c>
       <c r="AO21" s="9">
@@ -17626,7 +17626,7 @@
         <v>612470.39</v>
       </c>
       <c r="AX21" s="31">
-        <f>AD21*AP21</f>
+        <f>IF(E21="cancelled",0,AD21*AP21)</f>
         <v>3</v>
       </c>
       <c r="AY21" s="31">
@@ -17650,7 +17650,7 @@
         <v>612470.39</v>
       </c>
       <c r="BD21" s="31">
-        <f>AD21*AQ21</f>
+        <f>IF(E21="cancelled",0,AD21*AQ21)</f>
         <v>3</v>
       </c>
       <c r="BE21" s="31">
@@ -17674,7 +17674,7 @@
         <v>612470.39</v>
       </c>
       <c r="BJ21" s="31">
-        <f>AD21*AR21</f>
+        <f>IF(E21="cancelled",0,AD21*AR21)</f>
         <v>3</v>
       </c>
       <c r="BK21" s="31">
@@ -17848,7 +17848,7 @@
         <v>0</v>
       </c>
       <c r="AN22" s="9">
-        <f>AD22*T22</f>
+        <f>IF(E22="cancelled",0,AD22*T22)</f>
         <v>8</v>
       </c>
       <c r="AO22" s="9">
@@ -17888,7 +17888,7 @@
         <v>2370310.85</v>
       </c>
       <c r="AX22" s="31">
-        <f>AD22*AP22</f>
+        <f>IF(E22="cancelled",0,AD22*AP22)</f>
         <v>8</v>
       </c>
       <c r="AY22" s="31">
@@ -17912,7 +17912,7 @@
         <v>0</v>
       </c>
       <c r="BD22" s="31">
-        <f>AD22*AQ22</f>
+        <f>IF(E22="cancelled",0,AD22*AQ22)</f>
         <v>0</v>
       </c>
       <c r="BE22" s="31">
@@ -17936,7 +17936,7 @@
         <v>0</v>
       </c>
       <c r="BJ22" s="31">
-        <f>AD22*AR22</f>
+        <f>IF(E22="cancelled",0,AD22*AR22)</f>
         <v>0</v>
       </c>
       <c r="BK22" s="31">
@@ -18110,7 +18110,7 @@
         <v>11959870</v>
       </c>
       <c r="AN23" s="9">
-        <f>AD23*T23</f>
+        <f>IF(E23="cancelled",0,AD23*T23)</f>
         <v>7</v>
       </c>
       <c r="AO23" s="9">
@@ -18150,7 +18150,7 @@
         <v>2449611.94</v>
       </c>
       <c r="AX23" s="31">
-        <f>AD23*AP23</f>
+        <f>IF(E23="cancelled",0,AD23*AP23)</f>
         <v>7</v>
       </c>
       <c r="AY23" s="31">
@@ -18174,7 +18174,7 @@
         <v>2449611.94</v>
       </c>
       <c r="BD23" s="31">
-        <f>AD23*AQ23</f>
+        <f>IF(E23="cancelled",0,AD23*AQ23)</f>
         <v>7</v>
       </c>
       <c r="BE23" s="31">
@@ -18198,7 +18198,7 @@
         <v>2449611.94</v>
       </c>
       <c r="BJ23" s="31">
-        <f>AD23*AR23</f>
+        <f>IF(E23="cancelled",0,AD23*AR23)</f>
         <v>7</v>
       </c>
       <c r="BK23" s="31">
@@ -18372,7 +18372,7 @@
         <v>0</v>
       </c>
       <c r="AN24" s="9">
-        <f>AD24*T24</f>
+        <f>IF(E24="cancelled",0,AD24*T24)</f>
         <v>6</v>
       </c>
       <c r="AO24" s="9">
@@ -18412,7 +18412,7 @@
         <v>1618275.2200000002</v>
       </c>
       <c r="AX24" s="31">
-        <f>AD24*AP24</f>
+        <f>IF(E24="cancelled",0,AD24*AP24)</f>
         <v>6</v>
       </c>
       <c r="AY24" s="31">
@@ -18436,7 +18436,7 @@
         <v>0</v>
       </c>
       <c r="BD24" s="31">
-        <f>AD24*AQ24</f>
+        <f>IF(E24="cancelled",0,AD24*AQ24)</f>
         <v>0</v>
       </c>
       <c r="BE24" s="31">
@@ -18460,7 +18460,7 @@
         <v>0</v>
       </c>
       <c r="BJ24" s="31">
-        <f>AD24*AR24</f>
+        <f>IF(E24="cancelled",0,AD24*AR24)</f>
         <v>0</v>
       </c>
       <c r="BK24" s="31">
@@ -18634,7 +18634,7 @@
         <v>8362426</v>
       </c>
       <c r="AN25" s="9">
-        <f>AD25*T25</f>
+        <f>IF(E25="cancelled",0,AD25*T25)</f>
         <v>3</v>
       </c>
       <c r="AO25" s="9">
@@ -18674,7 +18674,7 @@
         <v>1967629.6</v>
       </c>
       <c r="AX25" s="31">
-        <f>AD25*AP25</f>
+        <f>IF(E25="cancelled",0,AD25*AP25)</f>
         <v>3</v>
       </c>
       <c r="AY25" s="31">
@@ -18698,7 +18698,7 @@
         <v>1967629.6</v>
       </c>
       <c r="BD25" s="31">
-        <f>AD25*AQ25</f>
+        <f>IF(E25="cancelled",0,AD25*AQ25)</f>
         <v>3</v>
       </c>
       <c r="BE25" s="31">
@@ -18722,7 +18722,7 @@
         <v>0</v>
       </c>
       <c r="BJ25" s="31">
-        <f>AD25*AR25</f>
+        <f>IF(E25="cancelled",0,AD25*AR25)</f>
         <v>0</v>
       </c>
       <c r="BK25" s="31">
@@ -18896,7 +18896,7 @@
         <v>0</v>
       </c>
       <c r="AN26" s="9">
-        <f>AD26*T26</f>
+        <f>IF(E26="cancelled",0,AD26*T26)</f>
         <v>7</v>
       </c>
       <c r="AO26" s="9">
@@ -18936,7 +18936,7 @@
         <v>1596119.8</v>
       </c>
       <c r="AX26" s="31">
-        <f>AD26*AP26</f>
+        <f>IF(E26="cancelled",0,AD26*AP26)</f>
         <v>7</v>
       </c>
       <c r="AY26" s="31">
@@ -18960,7 +18960,7 @@
         <v>0</v>
       </c>
       <c r="BD26" s="31">
-        <f>AD26*AQ26</f>
+        <f>IF(E26="cancelled",0,AD26*AQ26)</f>
         <v>0</v>
       </c>
       <c r="BE26" s="31">
@@ -18984,7 +18984,7 @@
         <v>0</v>
       </c>
       <c r="BJ26" s="31">
-        <f>AD26*AR26</f>
+        <f>IF(E26="cancelled",0,AD26*AR26)</f>
         <v>0</v>
       </c>
       <c r="BK26" s="31">
@@ -19158,7 +19158,7 @@
         <v>10203970</v>
       </c>
       <c r="AN27" s="9">
-        <f>AD27*T27</f>
+        <f>IF(E27="cancelled",0,AD27*T27)</f>
         <v>4</v>
       </c>
       <c r="AO27" s="9">
@@ -19198,7 +19198,7 @@
         <v>1971221.57</v>
       </c>
       <c r="AX27" s="31">
-        <f>AD27*AP27</f>
+        <f>IF(E27="cancelled",0,AD27*AP27)</f>
         <v>4</v>
       </c>
       <c r="AY27" s="31">
@@ -19222,7 +19222,7 @@
         <v>1971221.57</v>
       </c>
       <c r="BD27" s="31">
-        <f>AD27*AQ27</f>
+        <f>IF(E27="cancelled",0,AD27*AQ27)</f>
         <v>4</v>
       </c>
       <c r="BE27" s="31">
@@ -19246,7 +19246,7 @@
         <v>0</v>
       </c>
       <c r="BJ27" s="31">
-        <f>AD27*AR27</f>
+        <f>IF(E27="cancelled",0,AD27*AR27)</f>
         <v>0</v>
       </c>
       <c r="BK27" s="31">
@@ -19420,7 +19420,7 @@
         <v>0</v>
       </c>
       <c r="AN28" s="9">
-        <f>AD28*T28</f>
+        <f>IF(E28="cancelled",0,AD28*T28)</f>
         <v>5</v>
       </c>
       <c r="AO28" s="9">
@@ -19460,7 +19460,7 @@
         <v>2862388.8000000003</v>
       </c>
       <c r="AX28" s="31">
-        <f>AD28*AP28</f>
+        <f>IF(E28="cancelled",0,AD28*AP28)</f>
         <v>5</v>
       </c>
       <c r="AY28" s="31">
@@ -19484,7 +19484,7 @@
         <v>0</v>
       </c>
       <c r="BD28" s="31">
-        <f>AD28*AQ28</f>
+        <f>IF(E28="cancelled",0,AD28*AQ28)</f>
         <v>0</v>
       </c>
       <c r="BE28" s="31">
@@ -19508,7 +19508,7 @@
         <v>0</v>
       </c>
       <c r="BJ28" s="31">
-        <f>AD28*AR28</f>
+        <f>IF(E28="cancelled",0,AD28*AR28)</f>
         <v>0</v>
       </c>
       <c r="BK28" s="31">
@@ -19682,7 +19682,7 @@
         <v>6328208</v>
       </c>
       <c r="AN29" s="9">
-        <f>AD29*T29</f>
+        <f>IF(E29="cancelled",0,AD29*T29)</f>
         <v>8</v>
       </c>
       <c r="AO29" s="9">
@@ -19722,7 +19722,7 @@
         <v>1488990.2000000002</v>
       </c>
       <c r="AX29" s="31">
-        <f>AD29*AP29</f>
+        <f>IF(E29="cancelled",0,AD29*AP29)</f>
         <v>8</v>
       </c>
       <c r="AY29" s="31">
@@ -19746,7 +19746,7 @@
         <v>1488990.2000000002</v>
       </c>
       <c r="BD29" s="31">
-        <f>AD29*AQ29</f>
+        <f>IF(E29="cancelled",0,AD29*AQ29)</f>
         <v>8</v>
       </c>
       <c r="BE29" s="31">
@@ -19770,7 +19770,7 @@
         <v>0</v>
       </c>
       <c r="BJ29" s="31">
-        <f>AD29*AR29</f>
+        <f>IF(E29="cancelled",0,AD29*AR29)</f>
         <v>0</v>
       </c>
       <c r="BK29" s="31">
@@ -19944,7 +19944,7 @@
         <v>0</v>
       </c>
       <c r="AN30" s="9">
-        <f>AD30*T30</f>
+        <f>IF(E30="cancelled",0,AD30*T30)</f>
         <v>6</v>
       </c>
       <c r="AO30" s="9">
@@ -19984,7 +19984,7 @@
         <v>893469.3400000001</v>
       </c>
       <c r="AX30" s="31">
-        <f>AD30*AP30</f>
+        <f>IF(E30="cancelled",0,AD30*AP30)</f>
         <v>6</v>
       </c>
       <c r="AY30" s="31">
@@ -20008,7 +20008,7 @@
         <v>0</v>
       </c>
       <c r="BD30" s="31">
-        <f>AD30*AQ30</f>
+        <f>IF(E30="cancelled",0,AD30*AQ30)</f>
         <v>0</v>
       </c>
       <c r="BE30" s="31">
@@ -20032,7 +20032,7 @@
         <v>0</v>
       </c>
       <c r="BJ30" s="31">
-        <f>AD30*AR30</f>
+        <f>IF(E30="cancelled",0,AD30*AR30)</f>
         <v>0</v>
       </c>
       <c r="BK30" s="31">
@@ -20206,7 +20206,7 @@
         <v>8602870</v>
       </c>
       <c r="AN31" s="9">
-        <f>AD31*T31</f>
+        <f>IF(E31="cancelled",0,AD31*T31)</f>
         <v>3</v>
       </c>
       <c r="AO31" s="9">
@@ -20246,7 +20246,7 @@
         <v>1762033.6800000002</v>
       </c>
       <c r="AX31" s="31">
-        <f>AD31*AP31</f>
+        <f>IF(E31="cancelled",0,AD31*AP31)</f>
         <v>3</v>
       </c>
       <c r="AY31" s="31">
@@ -20270,7 +20270,7 @@
         <v>1762033.6800000002</v>
       </c>
       <c r="BD31" s="31">
-        <f>AD31*AQ31</f>
+        <f>IF(E31="cancelled",0,AD31*AQ31)</f>
         <v>3</v>
       </c>
       <c r="BE31" s="31">
@@ -20294,7 +20294,7 @@
         <v>0</v>
       </c>
       <c r="BJ31" s="31">
-        <f>AD31*AR31</f>
+        <f>IF(E31="cancelled",0,AD31*AR31)</f>
         <v>0</v>
       </c>
       <c r="BK31" s="31">
@@ -20468,7 +20468,7 @@
         <v>0</v>
       </c>
       <c r="AN32" s="9">
-        <f>AD32*T32</f>
+        <f>IF(E32="cancelled",0,AD32*T32)</f>
         <v>3</v>
       </c>
       <c r="AO32" s="9">
@@ -20508,7 +20508,7 @@
         <v>2337591</v>
       </c>
       <c r="AX32" s="31">
-        <f>AD32*AP32</f>
+        <f>IF(E32="cancelled",0,AD32*AP32)</f>
         <v>3</v>
       </c>
       <c r="AY32" s="31">
@@ -20532,7 +20532,7 @@
         <v>0</v>
       </c>
       <c r="BD32" s="31">
-        <f>AD32*AQ32</f>
+        <f>IF(E32="cancelled",0,AD32*AQ32)</f>
         <v>0</v>
       </c>
       <c r="BE32" s="31">
@@ -20556,7 +20556,7 @@
         <v>0</v>
       </c>
       <c r="BJ32" s="31">
-        <f>AD32*AR32</f>
+        <f>IF(E32="cancelled",0,AD32*AR32)</f>
         <v>0</v>
       </c>
       <c r="BK32" s="31">
@@ -20730,7 +20730,7 @@
         <v>7058374</v>
       </c>
       <c r="AN33" s="9">
-        <f>AD33*T33</f>
+        <f>IF(E33="cancelled",0,AD33*T33)</f>
         <v>5</v>
       </c>
       <c r="AO33" s="9">
@@ -20770,7 +20770,7 @@
         <v>1604176</v>
       </c>
       <c r="AX33" s="31">
-        <f>AD33*AP33</f>
+        <f>IF(E33="cancelled",0,AD33*AP33)</f>
         <v>5</v>
       </c>
       <c r="AY33" s="31">
@@ -20794,7 +20794,7 @@
         <v>1604176</v>
       </c>
       <c r="BD33" s="31">
-        <f>AD33*AQ33</f>
+        <f>IF(E33="cancelled",0,AD33*AQ33)</f>
         <v>5</v>
       </c>
       <c r="BE33" s="31">
@@ -20818,7 +20818,7 @@
         <v>1604176</v>
       </c>
       <c r="BJ33" s="31">
-        <f>AD33*AR33</f>
+        <f>IF(E33="cancelled",0,AD33*AR33)</f>
         <v>5</v>
       </c>
       <c r="BK33" s="31">
@@ -20992,7 +20992,7 @@
         <v>0</v>
       </c>
       <c r="AN34" s="9">
-        <f>AD34*T34</f>
+        <f>IF(E34="cancelled",0,AD34*T34)</f>
         <v>7</v>
       </c>
       <c r="AO34" s="9">
@@ -21032,7 +21032,7 @@
         <v>2921274.6</v>
       </c>
       <c r="AX34" s="31">
-        <f>AD34*AP34</f>
+        <f>IF(E34="cancelled",0,AD34*AP34)</f>
         <v>7</v>
       </c>
       <c r="AY34" s="31">
@@ -21056,7 +21056,7 @@
         <v>0</v>
       </c>
       <c r="BD34" s="31">
-        <f>AD34*AQ34</f>
+        <f>IF(E34="cancelled",0,AD34*AQ34)</f>
         <v>0</v>
       </c>
       <c r="BE34" s="31">
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="BJ34" s="31">
-        <f>AD34*AR34</f>
+        <f>IF(E34="cancelled",0,AD34*AR34)</f>
         <v>0</v>
       </c>
       <c r="BK34" s="31">
@@ -21254,7 +21254,7 @@
         <v>0</v>
       </c>
       <c r="AN35" s="9">
-        <f>AD35*T35</f>
+        <f>IF(E35="cancelled",0,AD35*T35)</f>
         <v>0</v>
       </c>
       <c r="AO35" s="9">
@@ -21294,7 +21294,7 @@
         <v>0</v>
       </c>
       <c r="AX35" s="31">
-        <f>AD35*AP35</f>
+        <f>IF(E35="cancelled",0,AD35*AP35)</f>
         <v>0</v>
       </c>
       <c r="AY35" s="31">
@@ -21318,7 +21318,7 @@
         <v>0</v>
       </c>
       <c r="BD35" s="31">
-        <f>AD35*AQ35</f>
+        <f>IF(E35="cancelled",0,AD35*AQ35)</f>
         <v>0</v>
       </c>
       <c r="BE35" s="31">
@@ -21342,7 +21342,7 @@
         <v>0</v>
       </c>
       <c r="BJ35" s="31">
-        <f>AD35*AR35</f>
+        <f>IF(E35="cancelled",0,AD35*AR35)</f>
         <v>0</v>
       </c>
       <c r="BK35" s="31">
@@ -21516,7 +21516,7 @@
         <v>0</v>
       </c>
       <c r="AN36" s="9">
-        <f>AD36*T36</f>
+        <f>IF(E36="cancelled",0,AD36*T36)</f>
         <v>5</v>
       </c>
       <c r="AO36" s="9">
@@ -21556,7 +21556,7 @@
         <v>1545174.8800000001</v>
       </c>
       <c r="AX36" s="31">
-        <f>AD36*AP36</f>
+        <f>IF(E36="cancelled",0,AD36*AP36)</f>
         <v>5</v>
       </c>
       <c r="AY36" s="31">
@@ -21580,7 +21580,7 @@
         <v>1545174.8800000001</v>
       </c>
       <c r="BD36" s="31">
-        <f>AD36*AQ36</f>
+        <f>IF(E36="cancelled",0,AD36*AQ36)</f>
         <v>5</v>
       </c>
       <c r="BE36" s="31">
@@ -21604,7 +21604,7 @@
         <v>1545174.8800000001</v>
       </c>
       <c r="BJ36" s="31">
-        <f>AD36*AR36</f>
+        <f>IF(E36="cancelled",0,AD36*AR36)</f>
         <v>5</v>
       </c>
       <c r="BK36" s="31">
@@ -21778,7 +21778,7 @@
         <v>2640612</v>
       </c>
       <c r="AN37" s="9">
-        <f>AD37*T37</f>
+        <f>IF(E37="cancelled",0,AD37*T37)</f>
         <v>4</v>
       </c>
       <c r="AO37" s="9">
@@ -21818,7 +21818,7 @@
         <v>510118.32000000007</v>
       </c>
       <c r="AX37" s="31">
-        <f>AD37*AP37</f>
+        <f>IF(E37="cancelled",0,AD37*AP37)</f>
         <v>4</v>
       </c>
       <c r="AY37" s="31">
@@ -21842,7 +21842,7 @@
         <v>510118.32000000007</v>
       </c>
       <c r="BD37" s="31">
-        <f>AD37*AQ37</f>
+        <f>IF(E37="cancelled",0,AD37*AQ37)</f>
         <v>4</v>
       </c>
       <c r="BE37" s="31">
@@ -21866,7 +21866,7 @@
         <v>510118.32000000007</v>
       </c>
       <c r="BJ37" s="31">
-        <f>AD37*AR37</f>
+        <f>IF(E37="cancelled",0,AD37*AR37)</f>
         <v>4</v>
       </c>
       <c r="BK37" s="31">
@@ -22040,7 +22040,7 @@
         <v>0</v>
       </c>
       <c r="AN38" s="9">
-        <f>AD38*T38</f>
+        <f>IF(E38="cancelled",0,AD38*T38)</f>
         <v>3</v>
       </c>
       <c r="AO38" s="9">
@@ -22080,7 +22080,7 @@
         <v>2245530</v>
       </c>
       <c r="AX38" s="31">
-        <f>AD38*AP38</f>
+        <f>IF(E38="cancelled",0,AD38*AP38)</f>
         <v>3</v>
       </c>
       <c r="AY38" s="31">
@@ -22104,7 +22104,7 @@
         <v>0</v>
       </c>
       <c r="BD38" s="31">
-        <f>AD38*AQ38</f>
+        <f>IF(E38="cancelled",0,AD38*AQ38)</f>
         <v>0</v>
       </c>
       <c r="BE38" s="31">
@@ -22128,7 +22128,7 @@
         <v>0</v>
       </c>
       <c r="BJ38" s="31">
-        <f>AD38*AR38</f>
+        <f>IF(E38="cancelled",0,AD38*AR38)</f>
         <v>0</v>
       </c>
       <c r="BK38" s="31">
@@ -22302,7 +22302,7 @@
         <v>4649256</v>
       </c>
       <c r="AN39" s="9">
-        <f>AD39*T39</f>
+        <f>IF(E39="cancelled",0,AD39*T39)</f>
         <v>7</v>
       </c>
       <c r="AO39" s="9">
@@ -22342,7 +22342,7 @@
         <v>929851.2100000001</v>
       </c>
       <c r="AX39" s="31">
-        <f>AD39*AP39</f>
+        <f>IF(E39="cancelled",0,AD39*AP39)</f>
         <v>7</v>
       </c>
       <c r="AY39" s="31">
@@ -22366,7 +22366,7 @@
         <v>929851.2100000001</v>
       </c>
       <c r="BD39" s="31">
-        <f>AD39*AQ39</f>
+        <f>IF(E39="cancelled",0,AD39*AQ39)</f>
         <v>7</v>
       </c>
       <c r="BE39" s="31">
@@ -22390,7 +22390,7 @@
         <v>0</v>
       </c>
       <c r="BJ39" s="31">
-        <f>AD39*AR39</f>
+        <f>IF(E39="cancelled",0,AD39*AR39)</f>
         <v>0</v>
       </c>
       <c r="BK39" s="31">
@@ -22564,7 +22564,7 @@
         <v>0</v>
       </c>
       <c r="AN40" s="9">
-        <f>AD40*T40</f>
+        <f>IF(E40="cancelled",0,AD40*T40)</f>
         <v>6</v>
       </c>
       <c r="AO40" s="9">
@@ -22604,7 +22604,7 @@
         <v>2325929.6300000004</v>
       </c>
       <c r="AX40" s="31">
-        <f>AD40*AP40</f>
+        <f>IF(E40="cancelled",0,AD40*AP40)</f>
         <v>6</v>
       </c>
       <c r="AY40" s="31">
@@ -22628,7 +22628,7 @@
         <v>0</v>
       </c>
       <c r="BD40" s="31">
-        <f>AD40*AQ40</f>
+        <f>IF(E40="cancelled",0,AD40*AQ40)</f>
         <v>0</v>
       </c>
       <c r="BE40" s="31">
@@ -22652,7 +22652,7 @@
         <v>0</v>
       </c>
       <c r="BJ40" s="31">
-        <f>AD40*AR40</f>
+        <f>IF(E40="cancelled",0,AD40*AR40)</f>
         <v>0</v>
       </c>
       <c r="BK40" s="31">
@@ -22826,7 +22826,7 @@
         <v>7819170</v>
       </c>
       <c r="AN41" s="9">
-        <f>AD41*T41</f>
+        <f>IF(E41="cancelled",0,AD41*T41)</f>
         <v>7</v>
       </c>
       <c r="AO41" s="9">
@@ -22866,7 +22866,7 @@
         <v>1839804.6</v>
       </c>
       <c r="AX41" s="31">
-        <f>AD41*AP41</f>
+        <f>IF(E41="cancelled",0,AD41*AP41)</f>
         <v>7</v>
       </c>
       <c r="AY41" s="31">
@@ -22890,7 +22890,7 @@
         <v>1839804.6</v>
       </c>
       <c r="BD41" s="31">
-        <f>AD41*AQ41</f>
+        <f>IF(E41="cancelled",0,AD41*AQ41)</f>
         <v>7</v>
       </c>
       <c r="BE41" s="31">
@@ -22914,7 +22914,7 @@
         <v>0</v>
       </c>
       <c r="BJ41" s="31">
-        <f>AD41*AR41</f>
+        <f>IF(E41="cancelled",0,AD41*AR41)</f>
         <v>0</v>
       </c>
       <c r="BK41" s="31">
@@ -23088,7 +23088,7 @@
         <v>0</v>
       </c>
       <c r="AN42" s="9">
-        <f>AD42*T42</f>
+        <f>IF(E42="cancelled",0,AD42*T42)</f>
         <v>4</v>
       </c>
       <c r="AO42" s="9">
@@ -23128,7 +23128,7 @@
         <v>1507987.3800000001</v>
       </c>
       <c r="AX42" s="31">
-        <f>AD42*AP42</f>
+        <f>IF(E42="cancelled",0,AD42*AP42)</f>
         <v>4</v>
       </c>
       <c r="AY42" s="31">
@@ -23152,7 +23152,7 @@
         <v>0</v>
       </c>
       <c r="BD42" s="31">
-        <f>AD42*AQ42</f>
+        <f>IF(E42="cancelled",0,AD42*AQ42)</f>
         <v>0</v>
       </c>
       <c r="BE42" s="31">
@@ -23176,7 +23176,7 @@
         <v>0</v>
       </c>
       <c r="BJ42" s="31">
-        <f>AD42*AR42</f>
+        <f>IF(E42="cancelled",0,AD42*AR42)</f>
         <v>0</v>
       </c>
       <c r="BK42" s="31">
@@ -23350,7 +23350,7 @@
         <v>12201755</v>
       </c>
       <c r="AN43" s="9">
-        <f>AD43*T43</f>
+        <f>IF(E43="cancelled",0,AD43*T43)</f>
         <v>2</v>
       </c>
       <c r="AO43" s="9">
@@ -23390,7 +23390,7 @@
         <v>2871001.2</v>
       </c>
       <c r="AX43" s="31">
-        <f>AD43*AP43</f>
+        <f>IF(E43="cancelled",0,AD43*AP43)</f>
         <v>2</v>
       </c>
       <c r="AY43" s="31">
@@ -23414,7 +23414,7 @@
         <v>2871001.2</v>
       </c>
       <c r="BD43" s="31">
-        <f>AD43*AQ43</f>
+        <f>IF(E43="cancelled",0,AD43*AQ43)</f>
         <v>2</v>
       </c>
       <c r="BE43" s="31">
@@ -23438,7 +23438,7 @@
         <v>0</v>
       </c>
       <c r="BJ43" s="31">
-        <f>AD43*AR43</f>
+        <f>IF(E43="cancelled",0,AD43*AR43)</f>
         <v>0</v>
       </c>
       <c r="BK43" s="31">
@@ -23612,7 +23612,7 @@
         <v>0</v>
       </c>
       <c r="AN44" s="9">
-        <f>AD44*T44</f>
+        <f>IF(E44="cancelled",0,AD44*T44)</f>
         <v>5</v>
       </c>
       <c r="AO44" s="9">
@@ -23652,7 +23652,7 @@
         <v>1517456.4000000001</v>
       </c>
       <c r="AX44" s="31">
-        <f>AD44*AP44</f>
+        <f>IF(E44="cancelled",0,AD44*AP44)</f>
         <v>5</v>
       </c>
       <c r="AY44" s="31">
@@ -23676,7 +23676,7 @@
         <v>0</v>
       </c>
       <c r="BD44" s="31">
-        <f>AD44*AQ44</f>
+        <f>IF(E44="cancelled",0,AD44*AQ44)</f>
         <v>0</v>
       </c>
       <c r="BE44" s="31">
@@ -23700,7 +23700,7 @@
         <v>0</v>
       </c>
       <c r="BJ44" s="31">
-        <f>AD44*AR44</f>
+        <f>IF(E44="cancelled",0,AD44*AR44)</f>
         <v>0</v>
       </c>
       <c r="BK44" s="31">
@@ -23874,7 +23874,7 @@
         <v>5729286</v>
       </c>
       <c r="AN45" s="9">
-        <f>AD45*T45</f>
+        <f>IF(E45="cancelled",0,AD45*T45)</f>
         <v>8</v>
       </c>
       <c r="AO45" s="9">
@@ -23914,7 +23914,7 @@
         <v>1302110.4000000001</v>
       </c>
       <c r="AX45" s="31">
-        <f>AD45*AP45</f>
+        <f>IF(E45="cancelled",0,AD45*AP45)</f>
         <v>8</v>
       </c>
       <c r="AY45" s="31">
@@ -23938,7 +23938,7 @@
         <v>1302110.4000000001</v>
       </c>
       <c r="BD45" s="31">
-        <f>AD45*AQ45</f>
+        <f>IF(E45="cancelled",0,AD45*AQ45)</f>
         <v>8</v>
       </c>
       <c r="BE45" s="31">
@@ -23962,7 +23962,7 @@
         <v>1302110.4000000001</v>
       </c>
       <c r="BJ45" s="31">
-        <f>AD45*AR45</f>
+        <f>IF(E45="cancelled",0,AD45*AR45)</f>
         <v>8</v>
       </c>
       <c r="BK45" s="31">
@@ -24136,7 +24136,7 @@
         <v>0</v>
       </c>
       <c r="AN46" s="9">
-        <f>AD46*T46</f>
+        <f>IF(E46="cancelled",0,AD46*T46)</f>
         <v>6</v>
       </c>
       <c r="AO46" s="9">
@@ -24176,7 +24176,7 @@
         <v>1683397.29</v>
       </c>
       <c r="AX46" s="31">
-        <f>AD46*AP46</f>
+        <f>IF(E46="cancelled",0,AD46*AP46)</f>
         <v>6</v>
       </c>
       <c r="AY46" s="31">
@@ -24200,7 +24200,7 @@
         <v>0</v>
       </c>
       <c r="BD46" s="31">
-        <f>AD46*AQ46</f>
+        <f>IF(E46="cancelled",0,AD46*AQ46)</f>
         <v>0</v>
       </c>
       <c r="BE46" s="31">
@@ -24224,7 +24224,7 @@
         <v>0</v>
       </c>
       <c r="BJ46" s="31">
-        <f>AD46*AR46</f>
+        <f>IF(E46="cancelled",0,AD46*AR46)</f>
         <v>0</v>
       </c>
       <c r="BK46" s="31">
@@ -24398,7 +24398,7 @@
         <v>6502650</v>
       </c>
       <c r="AN47" s="9">
-        <f>AD47*T47</f>
+        <f>IF(E47="cancelled",0,AD47*T47)</f>
         <v>5</v>
       </c>
       <c r="AO47" s="9">
@@ -24438,7 +24438,7 @@
         <v>1477875</v>
       </c>
       <c r="AX47" s="31">
-        <f>AD47*AP47</f>
+        <f>IF(E47="cancelled",0,AD47*AP47)</f>
         <v>5</v>
       </c>
       <c r="AY47" s="31">
@@ -24462,7 +24462,7 @@
         <v>1477875</v>
       </c>
       <c r="BD47" s="31">
-        <f>AD47*AQ47</f>
+        <f>IF(E47="cancelled",0,AD47*AQ47)</f>
         <v>5</v>
       </c>
       <c r="BE47" s="31">
@@ -24486,7 +24486,7 @@
         <v>0</v>
       </c>
       <c r="BJ47" s="31">
-        <f>AD47*AR47</f>
+        <f>IF(E47="cancelled",0,AD47*AR47)</f>
         <v>0</v>
       </c>
       <c r="BK47" s="31">
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="AN48" s="9">
-        <f>AD48*T48</f>
+        <f>IF(E48="cancelled",0,AD48*T48)</f>
         <v>5</v>
       </c>
       <c r="AO48" s="9">
@@ -24700,7 +24700,7 @@
         <v>2410057.4</v>
       </c>
       <c r="AX48" s="31">
-        <f>AD48*AP48</f>
+        <f>IF(E48="cancelled",0,AD48*AP48)</f>
         <v>5</v>
       </c>
       <c r="AY48" s="31">
@@ -24724,7 +24724,7 @@
         <v>2410057.4</v>
       </c>
       <c r="BD48" s="31">
-        <f>AD48*AQ48</f>
+        <f>IF(E48="cancelled",0,AD48*AQ48)</f>
         <v>5</v>
       </c>
       <c r="BE48" s="31">
@@ -24748,7 +24748,7 @@
         <v>2410057.4</v>
       </c>
       <c r="BJ48" s="31">
-        <f>AD48*AR48</f>
+        <f>IF(E48="cancelled",0,AD48*AR48)</f>
         <v>5</v>
       </c>
       <c r="BK48" s="31">
@@ -24922,7 +24922,7 @@
         <v>12051685</v>
       </c>
       <c r="AN49" s="9">
-        <f>AD49*T49</f>
+        <f>IF(E49="cancelled",0,AD49*T49)</f>
         <v>8</v>
       </c>
       <c r="AO49" s="9">
@@ -24962,7 +24962,7 @@
         <v>2468417.5100000002</v>
       </c>
       <c r="AX49" s="31">
-        <f>AD49*AP49</f>
+        <f>IF(E49="cancelled",0,AD49*AP49)</f>
         <v>8</v>
       </c>
       <c r="AY49" s="31">
@@ -24986,7 +24986,7 @@
         <v>2468417.5100000002</v>
       </c>
       <c r="BD49" s="31">
-        <f>AD49*AQ49</f>
+        <f>IF(E49="cancelled",0,AD49*AQ49)</f>
         <v>8</v>
       </c>
       <c r="BE49" s="31">
@@ -25010,7 +25010,7 @@
         <v>0</v>
       </c>
       <c r="BJ49" s="31">
-        <f>AD49*AR49</f>
+        <f>IF(E49="cancelled",0,AD49*AR49)</f>
         <v>0</v>
       </c>
       <c r="BK49" s="31">
@@ -25184,7 +25184,7 @@
         <v>0</v>
       </c>
       <c r="AN50" s="9">
-        <f>AD50*T50</f>
+        <f>IF(E50="cancelled",0,AD50*T50)</f>
         <v>8</v>
       </c>
       <c r="AO50" s="9">
@@ -25224,7 +25224,7 @@
         <v>2223083.2</v>
       </c>
       <c r="AX50" s="31">
-        <f>AD50*AP50</f>
+        <f>IF(E50="cancelled",0,AD50*AP50)</f>
         <v>8</v>
       </c>
       <c r="AY50" s="31">
@@ -25248,7 +25248,7 @@
         <v>0</v>
       </c>
       <c r="BD50" s="31">
-        <f>AD50*AQ50</f>
+        <f>IF(E50="cancelled",0,AD50*AQ50)</f>
         <v>0</v>
       </c>
       <c r="BE50" s="31">
@@ -25272,7 +25272,7 @@
         <v>0</v>
       </c>
       <c r="BJ50" s="31">
-        <f>AD50*AR50</f>
+        <f>IF(E50="cancelled",0,AD50*AR50)</f>
         <v>0</v>
       </c>
       <c r="BK50" s="31">
@@ -25446,7 +25446,7 @@
         <v>6723326</v>
       </c>
       <c r="AN51" s="9">
-        <f>AD51*T51</f>
+        <f>IF(E51="cancelled",0,AD51*T51)</f>
         <v>5</v>
       </c>
       <c r="AO51" s="9">
@@ -25486,7 +25486,7 @@
         <v>1344665.1500000001</v>
       </c>
       <c r="AX51" s="31">
-        <f>AD51*AP51</f>
+        <f>IF(E51="cancelled",0,AD51*AP51)</f>
         <v>5</v>
       </c>
       <c r="AY51" s="31">
@@ -25510,7 +25510,7 @@
         <v>1344665.1500000001</v>
       </c>
       <c r="BD51" s="31">
-        <f>AD51*AQ51</f>
+        <f>IF(E51="cancelled",0,AD51*AQ51)</f>
         <v>5</v>
       </c>
       <c r="BE51" s="31">
@@ -25534,7 +25534,7 @@
         <v>0</v>
       </c>
       <c r="BJ51" s="31">
-        <f>AD51*AR51</f>
+        <f>IF(E51="cancelled",0,AD51*AR51)</f>
         <v>0</v>
       </c>
       <c r="BK51" s="31">
@@ -25708,7 +25708,7 @@
         <v>0</v>
       </c>
       <c r="AN52" s="9">
-        <f>AD52*T52</f>
+        <f>IF(E52="cancelled",0,AD52*T52)</f>
         <v>5</v>
       </c>
       <c r="AO52" s="9">
@@ -25748,7 +25748,7 @@
         <v>471618.93000000005</v>
       </c>
       <c r="AX52" s="31">
-        <f>AD52*AP52</f>
+        <f>IF(E52="cancelled",0,AD52*AP52)</f>
         <v>5</v>
       </c>
       <c r="AY52" s="31">
@@ -25772,7 +25772,7 @@
         <v>0</v>
       </c>
       <c r="BD52" s="31">
-        <f>AD52*AQ52</f>
+        <f>IF(E52="cancelled",0,AD52*AQ52)</f>
         <v>0</v>
       </c>
       <c r="BE52" s="31">
@@ -25796,7 +25796,7 @@
         <v>0</v>
       </c>
       <c r="BJ52" s="31">
-        <f>AD52*AR52</f>
+        <f>IF(E52="cancelled",0,AD52*AR52)</f>
         <v>0</v>
       </c>
       <c r="BK52" s="31">
@@ -25970,7 +25970,7 @@
         <v>9452250</v>
       </c>
       <c r="AN53" s="9">
-        <f>AD53*T53</f>
+        <f>IF(E53="cancelled",0,AD53*T53)</f>
         <v>6</v>
       </c>
       <c r="AO53" s="9">
@@ -26010,7 +26010,7 @@
         <v>1890449.9800000002</v>
       </c>
       <c r="AX53" s="31">
-        <f>AD53*AP53</f>
+        <f>IF(E53="cancelled",0,AD53*AP53)</f>
         <v>6</v>
       </c>
       <c r="AY53" s="31">
@@ -26034,7 +26034,7 @@
         <v>1890449.9800000002</v>
       </c>
       <c r="BD53" s="31">
-        <f>AD53*AQ53</f>
+        <f>IF(E53="cancelled",0,AD53*AQ53)</f>
         <v>6</v>
       </c>
       <c r="BE53" s="31">
@@ -26058,7 +26058,7 @@
         <v>1890449.9800000002</v>
       </c>
       <c r="BJ53" s="31">
-        <f>AD53*AR53</f>
+        <f>IF(E53="cancelled",0,AD53*AR53)</f>
         <v>6</v>
       </c>
       <c r="BK53" s="31">
@@ -26232,7 +26232,7 @@
         <v>0</v>
       </c>
       <c r="AN54" s="9">
-        <f>AD54*T54</f>
+        <f>IF(E54="cancelled",0,AD54*T54)</f>
         <v>7</v>
       </c>
       <c r="AO54" s="9">
@@ -26272,7 +26272,7 @@
         <v>2108158.1</v>
       </c>
       <c r="AX54" s="31">
-        <f>AD54*AP54</f>
+        <f>IF(E54="cancelled",0,AD54*AP54)</f>
         <v>7</v>
       </c>
       <c r="AY54" s="31">
@@ -26296,7 +26296,7 @@
         <v>2108158.1</v>
       </c>
       <c r="BD54" s="31">
-        <f>AD54*AQ54</f>
+        <f>IF(E54="cancelled",0,AD54*AQ54)</f>
         <v>7</v>
       </c>
       <c r="BE54" s="31">
@@ -26320,7 +26320,7 @@
         <v>2108158.1</v>
       </c>
       <c r="BJ54" s="31">
-        <f>AD54*AR54</f>
+        <f>IF(E54="cancelled",0,AD54*AR54)</f>
         <v>7</v>
       </c>
       <c r="BK54" s="31">
@@ -26494,7 +26494,7 @@
         <v>5847575</v>
       </c>
       <c r="AN55" s="9">
-        <f>AD55*T55</f>
+        <f>IF(E55="cancelled",0,AD55*T55)</f>
         <v>3</v>
       </c>
       <c r="AO55" s="9">
@@ -26534,7 +26534,7 @@
         <v>1197696.07</v>
       </c>
       <c r="AX55" s="31">
-        <f>AD55*AP55</f>
+        <f>IF(E55="cancelled",0,AD55*AP55)</f>
         <v>3</v>
       </c>
       <c r="AY55" s="31">
@@ -26558,7 +26558,7 @@
         <v>1197696.07</v>
       </c>
       <c r="BD55" s="31">
-        <f>AD55*AQ55</f>
+        <f>IF(E55="cancelled",0,AD55*AQ55)</f>
         <v>3</v>
       </c>
       <c r="BE55" s="31">
@@ -26582,7 +26582,7 @@
         <v>1197696.07</v>
       </c>
       <c r="BJ55" s="31">
-        <f>AD55*AR55</f>
+        <f>IF(E55="cancelled",0,AD55*AR55)</f>
         <v>3</v>
       </c>
       <c r="BK55" s="31">
@@ -26756,7 +26756,7 @@
         <v>0</v>
       </c>
       <c r="AN56" s="9">
-        <f>AD56*T56</f>
+        <f>IF(E56="cancelled",0,AD56*T56)</f>
         <v>8</v>
       </c>
       <c r="AO56" s="9">
@@ -26796,7 +26796,7 @@
         <v>1923902.07</v>
       </c>
       <c r="AX56" s="31">
-        <f>AD56*AP56</f>
+        <f>IF(E56="cancelled",0,AD56*AP56)</f>
         <v>8</v>
       </c>
       <c r="AY56" s="31">
@@ -26820,7 +26820,7 @@
         <v>1923902.07</v>
       </c>
       <c r="BD56" s="31">
-        <f>AD56*AQ56</f>
+        <f>IF(E56="cancelled",0,AD56*AQ56)</f>
         <v>8</v>
       </c>
       <c r="BE56" s="31">
@@ -26844,7 +26844,7 @@
         <v>1923902.07</v>
       </c>
       <c r="BJ56" s="31">
-        <f>AD56*AR56</f>
+        <f>IF(E56="cancelled",0,AD56*AR56)</f>
         <v>8</v>
       </c>
       <c r="BK56" s="31">
@@ -27018,7 +27018,7 @@
         <v>4949263</v>
       </c>
       <c r="AN57" s="9">
-        <f>AD57*T57</f>
+        <f>IF(E57="cancelled",0,AD57*T57)</f>
         <v>7</v>
       </c>
       <c r="AO57" s="9">
@@ -27058,7 +27058,7 @@
         <v>1124832.4000000001</v>
       </c>
       <c r="AX57" s="31">
-        <f>AD57*AP57</f>
+        <f>IF(E57="cancelled",0,AD57*AP57)</f>
         <v>7</v>
       </c>
       <c r="AY57" s="31">
@@ -27082,7 +27082,7 @@
         <v>1124832.4000000001</v>
       </c>
       <c r="BD57" s="31">
-        <f>AD57*AQ57</f>
+        <f>IF(E57="cancelled",0,AD57*AQ57)</f>
         <v>7</v>
       </c>
       <c r="BE57" s="31">
@@ -27106,7 +27106,7 @@
         <v>0</v>
       </c>
       <c r="BJ57" s="31">
-        <f>AD57*AR57</f>
+        <f>IF(E57="cancelled",0,AD57*AR57)</f>
         <v>0</v>
       </c>
       <c r="BK57" s="31">
@@ -27280,7 +27280,7 @@
         <v>0</v>
       </c>
       <c r="AN58" s="9">
-        <f>AD58*T58</f>
+        <f>IF(E58="cancelled",0,AD58*T58)</f>
         <v>6</v>
       </c>
       <c r="AO58" s="9">
@@ -27320,7 +27320,7 @@
         <v>1880425.7600000002</v>
       </c>
       <c r="AX58" s="31">
-        <f>AD58*AP58</f>
+        <f>IF(E58="cancelled",0,AD58*AP58)</f>
         <v>6</v>
       </c>
       <c r="AY58" s="31">
@@ -27344,7 +27344,7 @@
         <v>1880425.7600000002</v>
       </c>
       <c r="BD58" s="31">
-        <f>AD58*AQ58</f>
+        <f>IF(E58="cancelled",0,AD58*AQ58)</f>
         <v>6</v>
       </c>
       <c r="BE58" s="31">
@@ -27368,7 +27368,7 @@
         <v>1880425.7600000002</v>
       </c>
       <c r="BJ58" s="31">
-        <f>AD58*AR58</f>
+        <f>IF(E58="cancelled",0,AD58*AR58)</f>
         <v>6</v>
       </c>
       <c r="BK58" s="31">
@@ -27542,7 +27542,7 @@
         <v>9982213</v>
       </c>
       <c r="AN59" s="9">
-        <f>AD59*T59</f>
+        <f>IF(E59="cancelled",0,AD59*T59)</f>
         <v>2</v>
       </c>
       <c r="AO59" s="9">
@@ -27582,7 +27582,7 @@
         <v>2044549.7100000002</v>
       </c>
       <c r="AX59" s="31">
-        <f>AD59*AP59</f>
+        <f>IF(E59="cancelled",0,AD59*AP59)</f>
         <v>2</v>
       </c>
       <c r="AY59" s="31">
@@ -27606,7 +27606,7 @@
         <v>2044549.7100000002</v>
       </c>
       <c r="BD59" s="31">
-        <f>AD59*AQ59</f>
+        <f>IF(E59="cancelled",0,AD59*AQ59)</f>
         <v>2</v>
       </c>
       <c r="BE59" s="31">
@@ -27630,7 +27630,7 @@
         <v>2044549.7100000002</v>
       </c>
       <c r="BJ59" s="31">
-        <f>AD59*AR59</f>
+        <f>IF(E59="cancelled",0,AD59*AR59)</f>
         <v>2</v>
       </c>
       <c r="BK59" s="31">
@@ -27804,7 +27804,7 @@
         <v>0</v>
       </c>
       <c r="AN60" s="9">
-        <f>AD60*T60</f>
+        <f>IF(E60="cancelled",0,AD60*T60)</f>
         <v>4</v>
       </c>
       <c r="AO60" s="9">
@@ -27844,7 +27844,7 @@
         <v>940056.31</v>
       </c>
       <c r="AX60" s="31">
-        <f>AD60*AP60</f>
+        <f>IF(E60="cancelled",0,AD60*AP60)</f>
         <v>4</v>
       </c>
       <c r="AY60" s="31">
@@ -27868,7 +27868,7 @@
         <v>0</v>
       </c>
       <c r="BD60" s="31">
-        <f>AD60*AQ60</f>
+        <f>IF(E60="cancelled",0,AD60*AQ60)</f>
         <v>0</v>
       </c>
       <c r="BE60" s="31">
@@ -27892,7 +27892,7 @@
         <v>0</v>
       </c>
       <c r="BJ60" s="31">
-        <f>AD60*AR60</f>
+        <f>IF(E60="cancelled",0,AD60*AR60)</f>
         <v>0</v>
       </c>
       <c r="BK60" s="31">
@@ -28066,7 +28066,7 @@
         <v>11518702</v>
       </c>
       <c r="AN61" s="9">
-        <f>AD61*T61</f>
+        <f>IF(E61="cancelled",0,AD61*T61)</f>
         <v>8</v>
       </c>
       <c r="AO61" s="9">
@@ -28106,7 +28106,7 @@
         <v>2710282.8000000003</v>
       </c>
       <c r="AX61" s="31">
-        <f>AD61*AP61</f>
+        <f>IF(E61="cancelled",0,AD61*AP61)</f>
         <v>8</v>
       </c>
       <c r="AY61" s="31">
@@ -28130,7 +28130,7 @@
         <v>2710282.8000000003</v>
       </c>
       <c r="BD61" s="31">
-        <f>AD61*AQ61</f>
+        <f>IF(E61="cancelled",0,AD61*AQ61)</f>
         <v>8</v>
       </c>
       <c r="BE61" s="31">
@@ -28154,7 +28154,7 @@
         <v>0</v>
       </c>
       <c r="BJ61" s="31">
-        <f>AD61*AR61</f>
+        <f>IF(E61="cancelled",0,AD61*AR61)</f>
         <v>0</v>
       </c>
       <c r="BK61" s="31">
@@ -28328,7 +28328,7 @@
         <v>0</v>
       </c>
       <c r="AN62" s="9">
-        <f>AD62*T62</f>
+        <f>IF(E62="cancelled",0,AD62*T62)</f>
         <v>0</v>
       </c>
       <c r="AO62" s="9">
@@ -28368,7 +28368,7 @@
         <v>0</v>
       </c>
       <c r="AX62" s="31">
-        <f>AD62*AP62</f>
+        <f>IF(E62="cancelled",0,AD62*AP62)</f>
         <v>0</v>
       </c>
       <c r="AY62" s="31">
@@ -28392,7 +28392,7 @@
         <v>0</v>
       </c>
       <c r="BD62" s="31">
-        <f>AD62*AQ62</f>
+        <f>IF(E62="cancelled",0,AD62*AQ62)</f>
         <v>0</v>
       </c>
       <c r="BE62" s="31">
@@ -28416,7 +28416,7 @@
         <v>0</v>
       </c>
       <c r="BJ62" s="31">
-        <f>AD62*AR62</f>
+        <f>IF(E62="cancelled",0,AD62*AR62)</f>
         <v>0</v>
       </c>
       <c r="BK62" s="31">
@@ -28590,7 +28590,7 @@
         <v>9890327</v>
       </c>
       <c r="AN63" s="9">
-        <f>AD63*T63</f>
+        <f>IF(E63="cancelled",0,AD63*T63)</f>
         <v>2</v>
       </c>
       <c r="AO63" s="9">
@@ -28630,7 +28630,7 @@
         <v>1978065.4300000002</v>
       </c>
       <c r="AX63" s="31">
-        <f>AD63*AP63</f>
+        <f>IF(E63="cancelled",0,AD63*AP63)</f>
         <v>2</v>
       </c>
       <c r="AY63" s="31">
@@ -28654,7 +28654,7 @@
         <v>1978065.4300000002</v>
       </c>
       <c r="BD63" s="31">
-        <f>AD63*AQ63</f>
+        <f>IF(E63="cancelled",0,AD63*AQ63)</f>
         <v>2</v>
       </c>
       <c r="BE63" s="31">
@@ -28678,7 +28678,7 @@
         <v>1978065.4300000002</v>
       </c>
       <c r="BJ63" s="31">
-        <f>AD63*AR63</f>
+        <f>IF(E63="cancelled",0,AD63*AR63)</f>
         <v>2</v>
       </c>
       <c r="BK63" s="31">
@@ -28852,7 +28852,7 @@
         <v>0</v>
       </c>
       <c r="AN64" s="9">
-        <f>AD64*T64</f>
+        <f>IF(E64="cancelled",0,AD64*T64)</f>
         <v>7</v>
       </c>
       <c r="AO64" s="9">
@@ -28892,7 +28892,7 @@
         <v>1486646.6</v>
       </c>
       <c r="AX64" s="31">
-        <f>AD64*AP64</f>
+        <f>IF(E64="cancelled",0,AD64*AP64)</f>
         <v>7</v>
       </c>
       <c r="AY64" s="31">
@@ -28916,7 +28916,7 @@
         <v>0</v>
       </c>
       <c r="BD64" s="31">
-        <f>AD64*AQ64</f>
+        <f>IF(E64="cancelled",0,AD64*AQ64)</f>
         <v>0</v>
       </c>
       <c r="BE64" s="31">
@@ -28940,7 +28940,7 @@
         <v>0</v>
       </c>
       <c r="BJ64" s="31">
-        <f>AD64*AR64</f>
+        <f>IF(E64="cancelled",0,AD64*AR64)</f>
         <v>0</v>
       </c>
       <c r="BK64" s="31">
@@ -29114,7 +29114,7 @@
         <v>7410300</v>
       </c>
       <c r="AN65" s="9">
-        <f>AD65*T65</f>
+        <f>IF(E65="cancelled",0,AD65*T65)</f>
         <v>2</v>
       </c>
       <c r="AO65" s="9">
@@ -29154,7 +29154,7 @@
         <v>1482060</v>
       </c>
       <c r="AX65" s="31">
-        <f>AD65*AP65</f>
+        <f>IF(E65="cancelled",0,AD65*AP65)</f>
         <v>2</v>
       </c>
       <c r="AY65" s="31">
@@ -29178,7 +29178,7 @@
         <v>1482060</v>
       </c>
       <c r="BD65" s="31">
-        <f>AD65*AQ65</f>
+        <f>IF(E65="cancelled",0,AD65*AQ65)</f>
         <v>2</v>
       </c>
       <c r="BE65" s="31">
@@ -29202,7 +29202,7 @@
         <v>1482060</v>
       </c>
       <c r="BJ65" s="31">
-        <f>AD65*AR65</f>
+        <f>IF(E65="cancelled",0,AD65*AR65)</f>
         <v>2</v>
       </c>
       <c r="BK65" s="31">
@@ -29376,7 +29376,7 @@
         <v>0</v>
       </c>
       <c r="AN66" s="9">
-        <f>AD66*T66</f>
+        <f>IF(E66="cancelled",0,AD66*T66)</f>
         <v>8</v>
       </c>
       <c r="AO66" s="9">
@@ -29416,7 +29416,7 @@
         <v>2034328.6</v>
       </c>
       <c r="AX66" s="31">
-        <f>AD66*AP66</f>
+        <f>IF(E66="cancelled",0,AD66*AP66)</f>
         <v>8</v>
       </c>
       <c r="AY66" s="31">
@@ -29440,7 +29440,7 @@
         <v>0</v>
       </c>
       <c r="BD66" s="31">
-        <f>AD66*AQ66</f>
+        <f>IF(E66="cancelled",0,AD66*AQ66)</f>
         <v>0</v>
       </c>
       <c r="BE66" s="31">
@@ -29464,7 +29464,7 @@
         <v>0</v>
       </c>
       <c r="BJ66" s="31">
-        <f>AD66*AR66</f>
+        <f>IF(E66="cancelled",0,AD66*AR66)</f>
         <v>0</v>
       </c>
       <c r="BK66" s="31">
@@ -29638,7 +29638,7 @@
         <v>3163480</v>
       </c>
       <c r="AN67" s="9">
-        <f>AD67*T67</f>
+        <f>IF(E67="cancelled",0,AD67*T67)</f>
         <v>2</v>
       </c>
       <c r="AO67" s="9">
@@ -29678,7 +29678,7 @@
         <v>611126.88</v>
       </c>
       <c r="AX67" s="31">
-        <f>AD67*AP67</f>
+        <f>IF(E67="cancelled",0,AD67*AP67)</f>
         <v>2</v>
       </c>
       <c r="AY67" s="31">
@@ -29702,7 +29702,7 @@
         <v>611126.88</v>
       </c>
       <c r="BD67" s="31">
-        <f>AD67*AQ67</f>
+        <f>IF(E67="cancelled",0,AD67*AQ67)</f>
         <v>2</v>
       </c>
       <c r="BE67" s="31">
@@ -29726,7 +29726,7 @@
         <v>611126.88</v>
       </c>
       <c r="BJ67" s="31">
-        <f>AD67*AR67</f>
+        <f>IF(E67="cancelled",0,AD67*AR67)</f>
         <v>2</v>
       </c>
       <c r="BK67" s="31">
@@ -29900,7 +29900,7 @@
         <v>0</v>
       </c>
       <c r="AN68" s="9">
-        <f>AD68*T68</f>
+        <f>IF(E68="cancelled",0,AD68*T68)</f>
         <v>4</v>
       </c>
       <c r="AO68" s="9">
@@ -29940,7 +29940,7 @@
         <v>1347209.03</v>
       </c>
       <c r="AX68" s="31">
-        <f>AD68*AP68</f>
+        <f>IF(E68="cancelled",0,AD68*AP68)</f>
         <v>4</v>
       </c>
       <c r="AY68" s="31">
@@ -29964,7 +29964,7 @@
         <v>1347209.03</v>
       </c>
       <c r="BD68" s="31">
-        <f>AD68*AQ68</f>
+        <f>IF(E68="cancelled",0,AD68*AQ68)</f>
         <v>4</v>
       </c>
       <c r="BE68" s="31">
@@ -29988,7 +29988,7 @@
         <v>1347209.03</v>
       </c>
       <c r="BJ68" s="31">
-        <f>AD68*AR68</f>
+        <f>IF(E68="cancelled",0,AD68*AR68)</f>
         <v>4</v>
       </c>
       <c r="BK68" s="31">
@@ -30162,7 +30162,7 @@
         <v>12414755</v>
       </c>
       <c r="AN69" s="9">
-        <f>AD69*T69</f>
+        <f>IF(E69="cancelled",0,AD69*T69)</f>
         <v>5</v>
       </c>
       <c r="AO69" s="9">
@@ -30202,7 +30202,7 @@
         <v>2398304.9200000004</v>
       </c>
       <c r="AX69" s="31">
-        <f>AD69*AP69</f>
+        <f>IF(E69="cancelled",0,AD69*AP69)</f>
         <v>5</v>
       </c>
       <c r="AY69" s="31">
@@ -30226,7 +30226,7 @@
         <v>2398304.9200000004</v>
       </c>
       <c r="BD69" s="31">
-        <f>AD69*AQ69</f>
+        <f>IF(E69="cancelled",0,AD69*AQ69)</f>
         <v>5</v>
       </c>
       <c r="BE69" s="31">
@@ -30250,7 +30250,7 @@
         <v>2398304.9200000004</v>
       </c>
       <c r="BJ69" s="31">
-        <f>AD69*AR69</f>
+        <f>IF(E69="cancelled",0,AD69*AR69)</f>
         <v>5</v>
       </c>
       <c r="BK69" s="31">
@@ -30424,7 +30424,7 @@
         <v>0</v>
       </c>
       <c r="AN70" s="9">
-        <f>AD70*T70</f>
+        <f>IF(E70="cancelled",0,AD70*T70)</f>
         <v>7</v>
       </c>
       <c r="AO70" s="9">
@@ -30464,7 +30464,7 @@
         <v>1210530.56</v>
       </c>
       <c r="AX70" s="31">
-        <f>AD70*AP70</f>
+        <f>IF(E70="cancelled",0,AD70*AP70)</f>
         <v>7</v>
       </c>
       <c r="AY70" s="31">
@@ -30488,7 +30488,7 @@
         <v>0</v>
       </c>
       <c r="BD70" s="31">
-        <f>AD70*AQ70</f>
+        <f>IF(E70="cancelled",0,AD70*AQ70)</f>
         <v>0</v>
       </c>
       <c r="BE70" s="31">
@@ -30512,7 +30512,7 @@
         <v>0</v>
       </c>
       <c r="BJ70" s="31">
-        <f>AD70*AR70</f>
+        <f>IF(E70="cancelled",0,AD70*AR70)</f>
         <v>0</v>
       </c>
       <c r="BK70" s="31">
@@ -30686,7 +30686,7 @@
         <v>8652924</v>
       </c>
       <c r="AN71" s="9">
-        <f>AD71*T71</f>
+        <f>IF(E71="cancelled",0,AD71*T71)</f>
         <v>3</v>
       </c>
       <c r="AO71" s="9">
@@ -30726,7 +30726,7 @@
         <v>1772285.7000000002</v>
       </c>
       <c r="AX71" s="31">
-        <f>AD71*AP71</f>
+        <f>IF(E71="cancelled",0,AD71*AP71)</f>
         <v>3</v>
       </c>
       <c r="AY71" s="31">
@@ -30750,7 +30750,7 @@
         <v>1772285.7000000002</v>
       </c>
       <c r="BD71" s="31">
-        <f>AD71*AQ71</f>
+        <f>IF(E71="cancelled",0,AD71*AQ71)</f>
         <v>3</v>
       </c>
       <c r="BE71" s="31">
@@ -30774,7 +30774,7 @@
         <v>0</v>
       </c>
       <c r="BJ71" s="31">
-        <f>AD71*AR71</f>
+        <f>IF(E71="cancelled",0,AD71*AR71)</f>
         <v>0</v>
       </c>
       <c r="BK71" s="31">
@@ -30948,7 +30948,7 @@
         <v>0</v>
       </c>
       <c r="AN72" s="9">
-        <f>AD72*T72</f>
+        <f>IF(E72="cancelled",0,AD72*T72)</f>
         <v>7</v>
       </c>
       <c r="AO72" s="9">
@@ -30988,7 +30988,7 @@
         <v>1145158.4200000002</v>
       </c>
       <c r="AX72" s="31">
-        <f>AD72*AP72</f>
+        <f>IF(E72="cancelled",0,AD72*AP72)</f>
         <v>7</v>
       </c>
       <c r="AY72" s="31">
@@ -31012,7 +31012,7 @@
         <v>0</v>
       </c>
       <c r="BD72" s="31">
-        <f>AD72*AQ72</f>
+        <f>IF(E72="cancelled",0,AD72*AQ72)</f>
         <v>0</v>
       </c>
       <c r="BE72" s="31">
@@ -31036,7 +31036,7 @@
         <v>0</v>
       </c>
       <c r="BJ72" s="31">
-        <f>AD72*AR72</f>
+        <f>IF(E72="cancelled",0,AD72*AR72)</f>
         <v>0</v>
       </c>
       <c r="BK72" s="31">
@@ -31210,7 +31210,7 @@
         <v>0</v>
       </c>
       <c r="AN73" s="9">
-        <f>AD73*T73</f>
+        <f>IF(E73="cancelled",0,AD73*T73)</f>
         <v>0</v>
       </c>
       <c r="AO73" s="9">
@@ -31250,7 +31250,7 @@
         <v>0</v>
       </c>
       <c r="AX73" s="31">
-        <f>AD73*AP73</f>
+        <f>IF(E73="cancelled",0,AD73*AP73)</f>
         <v>0</v>
       </c>
       <c r="AY73" s="31">
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
       <c r="BD73" s="31">
-        <f>AD73*AQ73</f>
+        <f>IF(E73="cancelled",0,AD73*AQ73)</f>
         <v>0</v>
       </c>
       <c r="BE73" s="31">
@@ -31298,7 +31298,7 @@
         <v>0</v>
       </c>
       <c r="BJ73" s="31">
-        <f>AD73*AR73</f>
+        <f>IF(E73="cancelled",0,AD73*AR73)</f>
         <v>0</v>
       </c>
       <c r="BK73" s="31">
@@ -31472,7 +31472,7 @@
         <v>0</v>
       </c>
       <c r="AN74" s="9">
-        <f>AD74*T74</f>
+        <f>IF(E74="cancelled",0,AD74*T74)</f>
         <v>8</v>
       </c>
       <c r="AO74" s="9">
@@ -31512,7 +31512,7 @@
         <v>497759.83</v>
       </c>
       <c r="AX74" s="31">
-        <f>AD74*AP74</f>
+        <f>IF(E74="cancelled",0,AD74*AP74)</f>
         <v>8</v>
       </c>
       <c r="AY74" s="31">
@@ -31536,7 +31536,7 @@
         <v>497759.83</v>
       </c>
       <c r="BD74" s="31">
-        <f>AD74*AQ74</f>
+        <f>IF(E74="cancelled",0,AD74*AQ74)</f>
         <v>8</v>
       </c>
       <c r="BE74" s="31">
@@ -31560,7 +31560,7 @@
         <v>497759.83</v>
       </c>
       <c r="BJ74" s="31">
-        <f>AD74*AR74</f>
+        <f>IF(E74="cancelled",0,AD74*AR74)</f>
         <v>8</v>
       </c>
       <c r="BK74" s="31">
@@ -31734,7 +31734,7 @@
         <v>11607263</v>
       </c>
       <c r="AN75" s="9">
-        <f>AD75*T75</f>
+        <f>IF(E75="cancelled",0,AD75*T75)</f>
         <v>3</v>
       </c>
       <c r="AO75" s="9">
@@ -31774,7 +31774,7 @@
         <v>2321452.5100000002</v>
       </c>
       <c r="AX75" s="31">
-        <f>AD75*AP75</f>
+        <f>IF(E75="cancelled",0,AD75*AP75)</f>
         <v>3</v>
       </c>
       <c r="AY75" s="31">
@@ -31798,7 +31798,7 @@
         <v>2321452.5100000002</v>
       </c>
       <c r="BD75" s="31">
-        <f>AD75*AQ75</f>
+        <f>IF(E75="cancelled",0,AD75*AQ75)</f>
         <v>3</v>
       </c>
       <c r="BE75" s="31">
@@ -31822,7 +31822,7 @@
         <v>2321452.5100000002</v>
       </c>
       <c r="BJ75" s="31">
-        <f>AD75*AR75</f>
+        <f>IF(E75="cancelled",0,AD75*AR75)</f>
         <v>3</v>
       </c>
       <c r="BK75" s="31">
@@ -31996,7 +31996,7 @@
         <v>0</v>
       </c>
       <c r="AN76" s="9">
-        <f>AD76*T76</f>
+        <f>IF(E76="cancelled",0,AD76*T76)</f>
         <v>4</v>
       </c>
       <c r="AO76" s="9">
@@ -32036,7 +32036,7 @@
         <v>1258563.2100000002</v>
       </c>
       <c r="AX76" s="31">
-        <f>AD76*AP76</f>
+        <f>IF(E76="cancelled",0,AD76*AP76)</f>
         <v>4</v>
       </c>
       <c r="AY76" s="31">
@@ -32060,7 +32060,7 @@
         <v>0</v>
       </c>
       <c r="BD76" s="31">
-        <f>AD76*AQ76</f>
+        <f>IF(E76="cancelled",0,AD76*AQ76)</f>
         <v>0</v>
       </c>
       <c r="BE76" s="31">
@@ -32084,7 +32084,7 @@
         <v>0</v>
       </c>
       <c r="BJ76" s="31">
-        <f>AD76*AR76</f>
+        <f>IF(E76="cancelled",0,AD76*AR76)</f>
         <v>0</v>
       </c>
       <c r="BK76" s="31">
@@ -32258,7 +32258,7 @@
         <v>5755777</v>
       </c>
       <c r="AN77" s="9">
-        <f>AD77*T77</f>
+        <f>IF(E77="cancelled",0,AD77*T77)</f>
         <v>2</v>
       </c>
       <c r="AO77" s="9">
@@ -32298,7 +32298,7 @@
         <v>1178894.07</v>
       </c>
       <c r="AX77" s="31">
-        <f>AD77*AP77</f>
+        <f>IF(E77="cancelled",0,AD77*AP77)</f>
         <v>2</v>
       </c>
       <c r="AY77" s="31">
@@ -32322,7 +32322,7 @@
         <v>1178894.07</v>
       </c>
       <c r="BD77" s="31">
-        <f>AD77*AQ77</f>
+        <f>IF(E77="cancelled",0,AD77*AQ77)</f>
         <v>2</v>
       </c>
       <c r="BE77" s="31">
@@ -32346,7 +32346,7 @@
         <v>0</v>
       </c>
       <c r="BJ77" s="31">
-        <f>AD77*AR77</f>
+        <f>IF(E77="cancelled",0,AD77*AR77)</f>
         <v>0</v>
       </c>
       <c r="BK77" s="31">
@@ -32520,7 +32520,7 @@
         <v>0</v>
       </c>
       <c r="AN78" s="9">
-        <f>AD78*T78</f>
+        <f>IF(E78="cancelled",0,AD78*T78)</f>
         <v>5</v>
       </c>
       <c r="AO78" s="9">
@@ -32560,7 +32560,7 @@
         <v>1978056.4200000002</v>
       </c>
       <c r="AX78" s="31">
-        <f>AD78*AP78</f>
+        <f>IF(E78="cancelled",0,AD78*AP78)</f>
         <v>5</v>
       </c>
       <c r="AY78" s="31">
@@ -32584,7 +32584,7 @@
         <v>0</v>
       </c>
       <c r="BD78" s="31">
-        <f>AD78*AQ78</f>
+        <f>IF(E78="cancelled",0,AD78*AQ78)</f>
         <v>0</v>
       </c>
       <c r="BE78" s="31">
@@ -32608,7 +32608,7 @@
         <v>0</v>
       </c>
       <c r="BJ78" s="31">
-        <f>AD78*AR78</f>
+        <f>IF(E78="cancelled",0,AD78*AR78)</f>
         <v>0</v>
       </c>
       <c r="BK78" s="31">
@@ -32782,7 +32782,7 @@
         <v>5457173</v>
       </c>
       <c r="AN79" s="9">
-        <f>AD79*T79</f>
+        <f>IF(E79="cancelled",0,AD79*T79)</f>
         <v>7</v>
       </c>
       <c r="AO79" s="9">
@@ -32822,7 +32822,7 @@
         <v>1091434.51</v>
       </c>
       <c r="AX79" s="31">
-        <f>AD79*AP79</f>
+        <f>IF(E79="cancelled",0,AD79*AP79)</f>
         <v>7</v>
       </c>
       <c r="AY79" s="31">
@@ -32846,7 +32846,7 @@
         <v>1091434.51</v>
       </c>
       <c r="BD79" s="31">
-        <f>AD79*AQ79</f>
+        <f>IF(E79="cancelled",0,AD79*AQ79)</f>
         <v>7</v>
       </c>
       <c r="BE79" s="31">
@@ -32870,7 +32870,7 @@
         <v>1091434.51</v>
       </c>
       <c r="BJ79" s="31">
-        <f>AD79*AR79</f>
+        <f>IF(E79="cancelled",0,AD79*AR79)</f>
         <v>7</v>
       </c>
       <c r="BK79" s="31">
@@ -33044,7 +33044,7 @@
         <v>0</v>
       </c>
       <c r="AN80" s="9">
-        <f>AD80*T80</f>
+        <f>IF(E80="cancelled",0,AD80*T80)</f>
         <v>7</v>
       </c>
       <c r="AO80" s="9">
@@ -33084,7 +33084,7 @@
         <v>1708894.06</v>
       </c>
       <c r="AX80" s="31">
-        <f>AD80*AP80</f>
+        <f>IF(E80="cancelled",0,AD80*AP80)</f>
         <v>7</v>
       </c>
       <c r="AY80" s="31">
@@ -33108,7 +33108,7 @@
         <v>1708894.06</v>
       </c>
       <c r="BD80" s="31">
-        <f>AD80*AQ80</f>
+        <f>IF(E80="cancelled",0,AD80*AQ80)</f>
         <v>7</v>
       </c>
       <c r="BE80" s="31">
@@ -33132,7 +33132,7 @@
         <v>1708894.06</v>
       </c>
       <c r="BJ80" s="31">
-        <f>AD80*AR80</f>
+        <f>IF(E80="cancelled",0,AD80*AR80)</f>
         <v>7</v>
       </c>
       <c r="BK80" s="31">
@@ -33306,7 +33306,7 @@
         <v>5192436</v>
       </c>
       <c r="AN81" s="9">
-        <f>AD81*T81</f>
+        <f>IF(E81="cancelled",0,AD81*T81)</f>
         <v>8</v>
       </c>
       <c r="AO81" s="9">
@@ -33346,7 +33346,7 @@
         <v>1180099</v>
       </c>
       <c r="AX81" s="31">
-        <f>AD81*AP81</f>
+        <f>IF(E81="cancelled",0,AD81*AP81)</f>
         <v>8</v>
       </c>
       <c r="AY81" s="31">
@@ -33370,7 +33370,7 @@
         <v>1180099</v>
       </c>
       <c r="BD81" s="31">
-        <f>AD81*AQ81</f>
+        <f>IF(E81="cancelled",0,AD81*AQ81)</f>
         <v>8</v>
       </c>
       <c r="BE81" s="31">
@@ -33394,7 +33394,7 @@
         <v>0</v>
       </c>
       <c r="BJ81" s="31">
-        <f>AD81*AR81</f>
+        <f>IF(E81="cancelled",0,AD81*AR81)</f>
         <v>0</v>
       </c>
       <c r="BK81" s="31">
@@ -33568,7 +33568,7 @@
         <v>0</v>
       </c>
       <c r="AN82" s="9">
-        <f>AD82*T82</f>
+        <f>IF(E82="cancelled",0,AD82*T82)</f>
         <v>4</v>
       </c>
       <c r="AO82" s="9">
@@ -33608,7 +33608,7 @@
         <v>485535.98000000004</v>
       </c>
       <c r="AX82" s="31">
-        <f>AD82*AP82</f>
+        <f>IF(E82="cancelled",0,AD82*AP82)</f>
         <v>4</v>
       </c>
       <c r="AY82" s="31">
@@ -33632,7 +33632,7 @@
         <v>485535.98000000004</v>
       </c>
       <c r="BD82" s="31">
-        <f>AD82*AQ82</f>
+        <f>IF(E82="cancelled",0,AD82*AQ82)</f>
         <v>4</v>
       </c>
       <c r="BE82" s="31">
@@ -33656,7 +33656,7 @@
         <v>485535.98000000004</v>
       </c>
       <c r="BJ82" s="31">
-        <f>AD82*AR82</f>
+        <f>IF(E82="cancelled",0,AD82*AR82)</f>
         <v>4</v>
       </c>
       <c r="BK82" s="31">
@@ -33830,7 +33830,7 @@
         <v>3302065</v>
       </c>
       <c r="AN83" s="9">
-        <f>AD83*T83</f>
+        <f>IF(E83="cancelled",0,AD83*T83)</f>
         <v>7</v>
       </c>
       <c r="AO83" s="9">
@@ -33870,7 +33870,7 @@
         <v>795678.2000000001</v>
       </c>
       <c r="AX83" s="31">
-        <f>AD83*AP83</f>
+        <f>IF(E83="cancelled",0,AD83*AP83)</f>
         <v>7</v>
       </c>
       <c r="AY83" s="31">
@@ -33894,7 +33894,7 @@
         <v>795678.2000000001</v>
       </c>
       <c r="BD83" s="31">
-        <f>AD83*AQ83</f>
+        <f>IF(E83="cancelled",0,AD83*AQ83)</f>
         <v>7</v>
       </c>
       <c r="BE83" s="31">
@@ -33918,7 +33918,7 @@
         <v>0</v>
       </c>
       <c r="BJ83" s="31">
-        <f>AD83*AR83</f>
+        <f>IF(E83="cancelled",0,AD83*AR83)</f>
         <v>0</v>
       </c>
       <c r="BK83" s="31">
@@ -34092,7 +34092,7 @@
         <v>0</v>
       </c>
       <c r="AN84" s="9">
-        <f>AD84*T84</f>
+        <f>IF(E84="cancelled",0,AD84*T84)</f>
         <v>5</v>
       </c>
       <c r="AO84" s="9">
@@ -34132,7 +34132,7 @@
         <v>2198877.0700000003</v>
       </c>
       <c r="AX84" s="31">
-        <f>AD84*AP84</f>
+        <f>IF(E84="cancelled",0,AD84*AP84)</f>
         <v>5</v>
       </c>
       <c r="AY84" s="31">
@@ -34156,7 +34156,7 @@
         <v>2198877.0700000003</v>
       </c>
       <c r="BD84" s="31">
-        <f>AD84*AQ84</f>
+        <f>IF(E84="cancelled",0,AD84*AQ84)</f>
         <v>5</v>
       </c>
       <c r="BE84" s="31">
@@ -34180,7 +34180,7 @@
         <v>2198877.0700000003</v>
       </c>
       <c r="BJ84" s="31">
-        <f>AD84*AR84</f>
+        <f>IF(E84="cancelled",0,AD84*AR84)</f>
         <v>5</v>
       </c>
       <c r="BK84" s="31">
@@ -34354,7 +34354,7 @@
         <v>8443124</v>
       </c>
       <c r="AN85" s="9">
-        <f>AD85*T85</f>
+        <f>IF(E85="cancelled",0,AD85*T85)</f>
         <v>5</v>
       </c>
       <c r="AO85" s="9">
@@ -34394,7 +34394,7 @@
         <v>2034487.8</v>
       </c>
       <c r="AX85" s="31">
-        <f>AD85*AP85</f>
+        <f>IF(E85="cancelled",0,AD85*AP85)</f>
         <v>5</v>
       </c>
       <c r="AY85" s="31">
@@ -34418,7 +34418,7 @@
         <v>2034487.8</v>
       </c>
       <c r="BD85" s="31">
-        <f>AD85*AQ85</f>
+        <f>IF(E85="cancelled",0,AD85*AQ85)</f>
         <v>5</v>
       </c>
       <c r="BE85" s="31">
@@ -34442,7 +34442,7 @@
         <v>2034487.8</v>
       </c>
       <c r="BJ85" s="31">
-        <f>AD85*AR85</f>
+        <f>IF(E85="cancelled",0,AD85*AR85)</f>
         <v>5</v>
       </c>
       <c r="BK85" s="31">
@@ -34616,7 +34616,7 @@
         <v>0</v>
       </c>
       <c r="AN86" s="9">
-        <f>AD86*T86</f>
+        <f>IF(E86="cancelled",0,AD86*T86)</f>
         <v>7</v>
       </c>
       <c r="AO86" s="9">
@@ -34656,7 +34656,7 @@
         <v>2389984.7800000003</v>
       </c>
       <c r="AX86" s="31">
-        <f>AD86*AP86</f>
+        <f>IF(E86="cancelled",0,AD86*AP86)</f>
         <v>7</v>
       </c>
       <c r="AY86" s="31">
@@ -34680,7 +34680,7 @@
         <v>0</v>
       </c>
       <c r="BD86" s="31">
-        <f>AD86*AQ86</f>
+        <f>IF(E86="cancelled",0,AD86*AQ86)</f>
         <v>0</v>
       </c>
       <c r="BE86" s="31">
@@ -34704,7 +34704,7 @@
         <v>0</v>
       </c>
       <c r="BJ86" s="31">
-        <f>AD86*AR86</f>
+        <f>IF(E86="cancelled",0,AD86*AR86)</f>
         <v>0</v>
       </c>
       <c r="BK86" s="31">
@@ -34878,7 +34878,7 @@
         <v>10221120</v>
       </c>
       <c r="AN87" s="9">
-        <f>AD87*T87</f>
+        <f>IF(E87="cancelled",0,AD87*T87)</f>
         <v>7</v>
       </c>
       <c r="AO87" s="9">
@@ -34918,7 +34918,7 @@
         <v>2044223.9900000002</v>
       </c>
       <c r="AX87" s="31">
-        <f>AD87*AP87</f>
+        <f>IF(E87="cancelled",0,AD87*AP87)</f>
         <v>7</v>
       </c>
       <c r="AY87" s="31">
@@ -34942,7 +34942,7 @@
         <v>2044223.9900000002</v>
       </c>
       <c r="BD87" s="31">
-        <f>AD87*AQ87</f>
+        <f>IF(E87="cancelled",0,AD87*AQ87)</f>
         <v>7</v>
       </c>
       <c r="BE87" s="31">
@@ -34966,7 +34966,7 @@
         <v>0</v>
       </c>
       <c r="BJ87" s="31">
-        <f>AD87*AR87</f>
+        <f>IF(E87="cancelled",0,AD87*AR87)</f>
         <v>0</v>
       </c>
       <c r="BK87" s="31">
@@ -35140,7 +35140,7 @@
         <v>0</v>
       </c>
       <c r="AN88" s="9">
-        <f>AD88*T88</f>
+        <f>IF(E88="cancelled",0,AD88*T88)</f>
         <v>5</v>
       </c>
       <c r="AO88" s="9">
@@ -35180,7 +35180,7 @@
         <v>1196275.04</v>
       </c>
       <c r="AX88" s="31">
-        <f>AD88*AP88</f>
+        <f>IF(E88="cancelled",0,AD88*AP88)</f>
         <v>5</v>
       </c>
       <c r="AY88" s="31">
@@ -35204,7 +35204,7 @@
         <v>1196275.04</v>
       </c>
       <c r="BD88" s="31">
-        <f>AD88*AQ88</f>
+        <f>IF(E88="cancelled",0,AD88*AQ88)</f>
         <v>5</v>
       </c>
       <c r="BE88" s="31">
@@ -35228,7 +35228,7 @@
         <v>1196275.04</v>
       </c>
       <c r="BJ88" s="31">
-        <f>AD88*AR88</f>
+        <f>IF(E88="cancelled",0,AD88*AR88)</f>
         <v>5</v>
       </c>
       <c r="BK88" s="31">
@@ -35402,7 +35402,7 @@
         <v>10674143</v>
       </c>
       <c r="AN89" s="9">
-        <f>AD89*T89</f>
+        <f>IF(E89="cancelled",0,AD89*T89)</f>
         <v>8</v>
       </c>
       <c r="AO89" s="9">
@@ -35442,7 +35442,7 @@
         <v>2186270.21</v>
       </c>
       <c r="AX89" s="31">
-        <f>AD89*AP89</f>
+        <f>IF(E89="cancelled",0,AD89*AP89)</f>
         <v>8</v>
       </c>
       <c r="AY89" s="31">
@@ -35466,7 +35466,7 @@
         <v>2186270.21</v>
       </c>
       <c r="BD89" s="31">
-        <f>AD89*AQ89</f>
+        <f>IF(E89="cancelled",0,AD89*AQ89)</f>
         <v>8</v>
       </c>
       <c r="BE89" s="31">
@@ -35490,7 +35490,7 @@
         <v>0</v>
       </c>
       <c r="BJ89" s="31">
-        <f>AD89*AR89</f>
+        <f>IF(E89="cancelled",0,AD89*AR89)</f>
         <v>0</v>
       </c>
       <c r="BK89" s="31">
@@ -35664,7 +35664,7 @@
         <v>0</v>
       </c>
       <c r="AN90" s="9">
-        <f>AD90*T90</f>
+        <f>IF(E90="cancelled",0,AD90*T90)</f>
         <v>8</v>
       </c>
       <c r="AO90" s="9">
@@ -35704,7 +35704,7 @@
         <v>1957732.7500000002</v>
       </c>
       <c r="AX90" s="31">
-        <f>AD90*AP90</f>
+        <f>IF(E90="cancelled",0,AD90*AP90)</f>
         <v>8</v>
       </c>
       <c r="AY90" s="31">
@@ -35728,7 +35728,7 @@
         <v>1957732.7500000002</v>
       </c>
       <c r="BD90" s="31">
-        <f>AD90*AQ90</f>
+        <f>IF(E90="cancelled",0,AD90*AQ90)</f>
         <v>8</v>
       </c>
       <c r="BE90" s="31">
@@ -35752,7 +35752,7 @@
         <v>1957732.7500000002</v>
       </c>
       <c r="BJ90" s="31">
-        <f>AD90*AR90</f>
+        <f>IF(E90="cancelled",0,AD90*AR90)</f>
         <v>8</v>
       </c>
       <c r="BK90" s="31">
@@ -35926,7 +35926,7 @@
         <v>4973557</v>
       </c>
       <c r="AN91" s="9">
-        <f>AD91*T91</f>
+        <f>IF(E91="cancelled",0,AD91*T91)</f>
         <v>5</v>
       </c>
       <c r="AO91" s="9">
@@ -35966,7 +35966,7 @@
         <v>994711.31</v>
       </c>
       <c r="AX91" s="31">
-        <f>AD91*AP91</f>
+        <f>IF(E91="cancelled",0,AD91*AP91)</f>
         <v>5</v>
       </c>
       <c r="AY91" s="31">
@@ -35990,7 +35990,7 @@
         <v>994711.31</v>
       </c>
       <c r="BD91" s="31">
-        <f>AD91*AQ91</f>
+        <f>IF(E91="cancelled",0,AD91*AQ91)</f>
         <v>5</v>
       </c>
       <c r="BE91" s="31">
@@ -36014,7 +36014,7 @@
         <v>0</v>
       </c>
       <c r="BJ91" s="31">
-        <f>AD91*AR91</f>
+        <f>IF(E91="cancelled",0,AD91*AR91)</f>
         <v>0</v>
       </c>
       <c r="BK91" s="31">
@@ -36188,7 +36188,7 @@
         <v>0</v>
       </c>
       <c r="AN92" s="9">
-        <f>AD92*T92</f>
+        <f>IF(E92="cancelled",0,AD92*T92)</f>
         <v>8</v>
       </c>
       <c r="AO92" s="9">
@@ -36228,7 +36228,7 @@
         <v>1907482.11</v>
       </c>
       <c r="AX92" s="31">
-        <f>AD92*AP92</f>
+        <f>IF(E92="cancelled",0,AD92*AP92)</f>
         <v>8</v>
       </c>
       <c r="AY92" s="31">
@@ -36252,7 +36252,7 @@
         <v>0</v>
       </c>
       <c r="BD92" s="31">
-        <f>AD92*AQ92</f>
+        <f>IF(E92="cancelled",0,AD92*AQ92)</f>
         <v>0</v>
       </c>
       <c r="BE92" s="31">
@@ -36276,7 +36276,7 @@
         <v>0</v>
       </c>
       <c r="BJ92" s="31">
-        <f>AD92*AR92</f>
+        <f>IF(E92="cancelled",0,AD92*AR92)</f>
         <v>0</v>
       </c>
       <c r="BK92" s="31">
@@ -36450,7 +36450,7 @@
         <v>12004933</v>
       </c>
       <c r="AN93" s="9">
-        <f>AD93*T93</f>
+        <f>IF(E93="cancelled",0,AD93*T93)</f>
         <v>7</v>
       </c>
       <c r="AO93" s="9">
@@ -36490,7 +36490,7 @@
         <v>2400986.6700000004</v>
       </c>
       <c r="AX93" s="31">
-        <f>AD93*AP93</f>
+        <f>IF(E93="cancelled",0,AD93*AP93)</f>
         <v>7</v>
       </c>
       <c r="AY93" s="31">
@@ -36514,7 +36514,7 @@
         <v>2400986.6700000004</v>
       </c>
       <c r="BD93" s="31">
-        <f>AD93*AQ93</f>
+        <f>IF(E93="cancelled",0,AD93*AQ93)</f>
         <v>7</v>
       </c>
       <c r="BE93" s="31">
@@ -36538,7 +36538,7 @@
         <v>0</v>
       </c>
       <c r="BJ93" s="31">
-        <f>AD93*AR93</f>
+        <f>IF(E93="cancelled",0,AD93*AR93)</f>
         <v>0</v>
       </c>
       <c r="BK93" s="31">
@@ -36712,7 +36712,7 @@
         <v>0</v>
       </c>
       <c r="AN94" s="9">
-        <f>AD94*T94</f>
+        <f>IF(E94="cancelled",0,AD94*T94)</f>
         <v>7</v>
       </c>
       <c r="AO94" s="9">
@@ -36752,7 +36752,7 @@
         <v>1193923.09</v>
       </c>
       <c r="AX94" s="31">
-        <f>AD94*AP94</f>
+        <f>IF(E94="cancelled",0,AD94*AP94)</f>
         <v>7</v>
       </c>
       <c r="AY94" s="31">
@@ -36776,7 +36776,7 @@
         <v>1193923.09</v>
       </c>
       <c r="BD94" s="31">
-        <f>AD94*AQ94</f>
+        <f>IF(E94="cancelled",0,AD94*AQ94)</f>
         <v>7</v>
       </c>
       <c r="BE94" s="31">
@@ -36800,7 +36800,7 @@
         <v>1193923.09</v>
       </c>
       <c r="BJ94" s="31">
-        <f>AD94*AR94</f>
+        <f>IF(E94="cancelled",0,AD94*AR94)</f>
         <v>7</v>
       </c>
       <c r="BK94" s="31">
@@ -36974,7 +36974,7 @@
         <v>3503240</v>
       </c>
       <c r="AN95" s="9">
-        <f>AD95*T95</f>
+        <f>IF(E95="cancelled",0,AD95*T95)</f>
         <v>7</v>
       </c>
       <c r="AO95" s="9">
@@ -37014,7 +37014,7 @@
         <v>796190.8</v>
       </c>
       <c r="AX95" s="31">
-        <f>AD95*AP95</f>
+        <f>IF(E95="cancelled",0,AD95*AP95)</f>
         <v>7</v>
       </c>
       <c r="AY95" s="31">
@@ -37038,7 +37038,7 @@
         <v>796190.8</v>
       </c>
       <c r="BD95" s="31">
-        <f>AD95*AQ95</f>
+        <f>IF(E95="cancelled",0,AD95*AQ95)</f>
         <v>7</v>
       </c>
       <c r="BE95" s="31">
@@ -37062,7 +37062,7 @@
         <v>0</v>
       </c>
       <c r="BJ95" s="31">
-        <f>AD95*AR95</f>
+        <f>IF(E95="cancelled",0,AD95*AR95)</f>
         <v>0</v>
       </c>
       <c r="BK95" s="31">
@@ -37236,7 +37236,7 @@
         <v>0</v>
       </c>
       <c r="AN96" s="9">
-        <f>AD96*T96</f>
+        <f>IF(E96="cancelled",0,AD96*T96)</f>
         <v>3</v>
       </c>
       <c r="AO96" s="9">
@@ -37276,7 +37276,7 @@
         <v>499278.95</v>
       </c>
       <c r="AX96" s="31">
-        <f>AD96*AP96</f>
+        <f>IF(E96="cancelled",0,AD96*AP96)</f>
         <v>3</v>
       </c>
       <c r="AY96" s="31">
@@ -37300,7 +37300,7 @@
         <v>0</v>
       </c>
       <c r="BD96" s="31">
-        <f>AD96*AQ96</f>
+        <f>IF(E96="cancelled",0,AD96*AQ96)</f>
         <v>0</v>
       </c>
       <c r="BE96" s="31">
@@ -37324,7 +37324,7 @@
         <v>0</v>
       </c>
       <c r="BJ96" s="31">
-        <f>AD96*AR96</f>
+        <f>IF(E96="cancelled",0,AD96*AR96)</f>
         <v>0</v>
       </c>
       <c r="BK96" s="31">
@@ -37498,7 +37498,7 @@
         <v>5957178</v>
       </c>
       <c r="AN97" s="9">
-        <f>AD97*T97</f>
+        <f>IF(E97="cancelled",0,AD97*T97)</f>
         <v>8</v>
       </c>
       <c r="AO97" s="9">
@@ -37538,7 +37538,7 @@
         <v>1191435.6500000001</v>
       </c>
       <c r="AX97" s="31">
-        <f>AD97*AP97</f>
+        <f>IF(E97="cancelled",0,AD97*AP97)</f>
         <v>8</v>
       </c>
       <c r="AY97" s="31">
@@ -37562,7 +37562,7 @@
         <v>1191435.6500000001</v>
       </c>
       <c r="BD97" s="31">
-        <f>AD97*AQ97</f>
+        <f>IF(E97="cancelled",0,AD97*AQ97)</f>
         <v>8</v>
       </c>
       <c r="BE97" s="31">
@@ -37586,7 +37586,7 @@
         <v>0</v>
       </c>
       <c r="BJ97" s="31">
-        <f>AD97*AR97</f>
+        <f>IF(E97="cancelled",0,AD97*AR97)</f>
         <v>0</v>
       </c>
       <c r="BK97" s="31">
@@ -37760,7 +37760,7 @@
         <v>0</v>
       </c>
       <c r="AN98" s="9">
-        <f>AD98*T98</f>
+        <f>IF(E98="cancelled",0,AD98*T98)</f>
         <v>3</v>
       </c>
       <c r="AO98" s="9">
@@ -37800,7 +37800,7 @@
         <v>932132.2000000001</v>
       </c>
       <c r="AX98" s="31">
-        <f>AD98*AP98</f>
+        <f>IF(E98="cancelled",0,AD98*AP98)</f>
         <v>3</v>
       </c>
       <c r="AY98" s="31">
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="BD98" s="31">
-        <f>AD98*AQ98</f>
+        <f>IF(E98="cancelled",0,AD98*AQ98)</f>
         <v>0</v>
       </c>
       <c r="BE98" s="31">
@@ -37848,7 +37848,7 @@
         <v>0</v>
       </c>
       <c r="BJ98" s="31">
-        <f>AD98*AR98</f>
+        <f>IF(E98="cancelled",0,AD98*AR98)</f>
         <v>0</v>
       </c>
       <c r="BK98" s="31">
@@ -38022,7 +38022,7 @@
         <v>10816943</v>
       </c>
       <c r="AN99" s="9">
-        <f>AD99*T99</f>
+        <f>IF(E99="cancelled",0,AD99*T99)</f>
         <v>4</v>
       </c>
       <c r="AO99" s="9">
@@ -38062,7 +38062,7 @@
         <v>2089636.7700000003</v>
       </c>
       <c r="AX99" s="31">
-        <f>AD99*AP99</f>
+        <f>IF(E99="cancelled",0,AD99*AP99)</f>
         <v>4</v>
       </c>
       <c r="AY99" s="31">
@@ -38086,7 +38086,7 @@
         <v>2089636.7700000003</v>
       </c>
       <c r="BD99" s="31">
-        <f>AD99*AQ99</f>
+        <f>IF(E99="cancelled",0,AD99*AQ99)</f>
         <v>4</v>
       </c>
       <c r="BE99" s="31">
@@ -38110,7 +38110,7 @@
         <v>0</v>
       </c>
       <c r="BJ99" s="31">
-        <f>AD99*AR99</f>
+        <f>IF(E99="cancelled",0,AD99*AR99)</f>
         <v>0</v>
       </c>
       <c r="BK99" s="31">
@@ -38284,7 +38284,7 @@
         <v>0</v>
       </c>
       <c r="AN100" s="9">
-        <f>AD100*T100</f>
+        <f>IF(E100="cancelled",0,AD100*T100)</f>
         <v>2</v>
       </c>
       <c r="AO100" s="9">
@@ -38324,7 +38324,7 @@
         <v>744730</v>
       </c>
       <c r="AX100" s="31">
-        <f>AD100*AP100</f>
+        <f>IF(E100="cancelled",0,AD100*AP100)</f>
         <v>2</v>
       </c>
       <c r="AY100" s="31">
@@ -38348,7 +38348,7 @@
         <v>0</v>
       </c>
       <c r="BD100" s="31">
-        <f>AD100*AQ100</f>
+        <f>IF(E100="cancelled",0,AD100*AQ100)</f>
         <v>0</v>
       </c>
       <c r="BE100" s="31">
@@ -38372,7 +38372,7 @@
         <v>0</v>
       </c>
       <c r="BJ100" s="31">
-        <f>AD100*AR100</f>
+        <f>IF(E100="cancelled",0,AD100*AR100)</f>
         <v>0</v>
       </c>
       <c r="BK100" s="31">
@@ -38546,7 +38546,7 @@
         <v>11763133</v>
       </c>
       <c r="AN101" s="9">
-        <f>AD101*T101</f>
+        <f>IF(E101="cancelled",0,AD101*T101)</f>
         <v>4</v>
       </c>
       <c r="AO101" s="9">
@@ -38586,7 +38586,7 @@
         <v>2673439.4000000004</v>
       </c>
       <c r="AX101" s="31">
-        <f>AD101*AP101</f>
+        <f>IF(E101="cancelled",0,AD101*AP101)</f>
         <v>4</v>
       </c>
       <c r="AY101" s="31">
@@ -38610,7 +38610,7 @@
         <v>2673439.4000000004</v>
       </c>
       <c r="BD101" s="31">
-        <f>AD101*AQ101</f>
+        <f>IF(E101="cancelled",0,AD101*AQ101)</f>
         <v>4</v>
       </c>
       <c r="BE101" s="31">
@@ -38634,7 +38634,7 @@
         <v>2673439.4000000004</v>
       </c>
       <c r="BJ101" s="31">
-        <f>AD101*AR101</f>
+        <f>IF(E101="cancelled",0,AD101*AR101)</f>
         <v>4</v>
       </c>
       <c r="BK101" s="31">
@@ -38808,7 +38808,7 @@
         <v>0</v>
       </c>
       <c r="AN102" s="9">
-        <f>AD102*T102</f>
+        <f>IF(E102="cancelled",0,AD102*T102)</f>
         <v>4</v>
       </c>
       <c r="AO102" s="9">
@@ -38848,7 +38848,7 @@
         <v>1465344.07</v>
       </c>
       <c r="AX102" s="31">
-        <f>AD102*AP102</f>
+        <f>IF(E102="cancelled",0,AD102*AP102)</f>
         <v>4</v>
       </c>
       <c r="AY102" s="31">
@@ -38872,7 +38872,7 @@
         <v>0</v>
       </c>
       <c r="BD102" s="31">
-        <f>AD102*AQ102</f>
+        <f>IF(E102="cancelled",0,AD102*AQ102)</f>
         <v>0</v>
       </c>
       <c r="BE102" s="31">
@@ -38896,7 +38896,7 @@
         <v>0</v>
       </c>
       <c r="BJ102" s="31">
-        <f>AD102*AR102</f>
+        <f>IF(E102="cancelled",0,AD102*AR102)</f>
         <v>0</v>
       </c>
       <c r="BK102" s="31">
@@ -39070,7 +39070,7 @@
         <v>3998667</v>
       </c>
       <c r="AN103" s="9">
-        <f>AD103*T103</f>
+        <f>IF(E103="cancelled",0,AD103*T103)</f>
         <v>4</v>
       </c>
       <c r="AO103" s="9">
@@ -39110,7 +39110,7 @@
         <v>662773.39</v>
       </c>
       <c r="AX103" s="31">
-        <f>AD103*AP103</f>
+        <f>IF(E103="cancelled",0,AD103*AP103)</f>
         <v>4</v>
       </c>
       <c r="AY103" s="31">
@@ -39134,7 +39134,7 @@
         <v>662773.39</v>
       </c>
       <c r="BD103" s="31">
-        <f>AD103*AQ103</f>
+        <f>IF(E103="cancelled",0,AD103*AQ103)</f>
         <v>4</v>
       </c>
       <c r="BE103" s="31">
@@ -39158,7 +39158,7 @@
         <v>0</v>
       </c>
       <c r="BJ103" s="31">
-        <f>AD103*AR103</f>
+        <f>IF(E103="cancelled",0,AD103*AR103)</f>
         <v>0</v>
       </c>
       <c r="BK103" s="31">
@@ -39332,7 +39332,7 @@
         <v>0</v>
       </c>
       <c r="AN104" s="9">
-        <f>AD104*T104</f>
+        <f>IF(E104="cancelled",0,AD104*T104)</f>
         <v>7</v>
       </c>
       <c r="AO104" s="9">
@@ -39372,7 +39372,7 @@
         <v>1730144.06</v>
       </c>
       <c r="AX104" s="31">
-        <f>AD104*AP104</f>
+        <f>IF(E104="cancelled",0,AD104*AP104)</f>
         <v>7</v>
       </c>
       <c r="AY104" s="31">
@@ -39396,7 +39396,7 @@
         <v>0</v>
       </c>
       <c r="BD104" s="31">
-        <f>AD104*AQ104</f>
+        <f>IF(E104="cancelled",0,AD104*AQ104)</f>
         <v>0</v>
       </c>
       <c r="BE104" s="31">
@@ -39420,7 +39420,7 @@
         <v>0</v>
       </c>
       <c r="BJ104" s="31">
-        <f>AD104*AR104</f>
+        <f>IF(E104="cancelled",0,AD104*AR104)</f>
         <v>0</v>
       </c>
       <c r="BK104" s="31">
@@ -39594,7 +39594,7 @@
         <v>9256372</v>
       </c>
       <c r="AN105" s="9">
-        <f>AD105*T105</f>
+        <f>IF(E105="cancelled",0,AD105*T105)</f>
         <v>4</v>
       </c>
       <c r="AO105" s="9">
@@ -39634,7 +39634,7 @@
         <v>1788162.85</v>
       </c>
       <c r="AX105" s="31">
-        <f>AD105*AP105</f>
+        <f>IF(E105="cancelled",0,AD105*AP105)</f>
         <v>4</v>
       </c>
       <c r="AY105" s="31">
@@ -39658,7 +39658,7 @@
         <v>1788162.85</v>
       </c>
       <c r="BD105" s="31">
-        <f>AD105*AQ105</f>
+        <f>IF(E105="cancelled",0,AD105*AQ105)</f>
         <v>4</v>
       </c>
       <c r="BE105" s="31">
@@ -39682,7 +39682,7 @@
         <v>1788162.85</v>
       </c>
       <c r="BJ105" s="31">
-        <f>AD105*AR105</f>
+        <f>IF(E105="cancelled",0,AD105*AR105)</f>
         <v>4</v>
       </c>
       <c r="BK105" s="31">
@@ -39856,7 +39856,7 @@
         <v>0</v>
       </c>
       <c r="AN106" s="9">
-        <f>AD106*T106</f>
+        <f>IF(E106="cancelled",0,AD106*T106)</f>
         <v>4</v>
       </c>
       <c r="AO106" s="9">
@@ -39896,7 +39896,7 @@
         <v>1878006.6600000001</v>
       </c>
       <c r="AX106" s="31">
-        <f>AD106*AP106</f>
+        <f>IF(E106="cancelled",0,AD106*AP106)</f>
         <v>4</v>
       </c>
       <c r="AY106" s="31">
@@ -39920,7 +39920,7 @@
         <v>0</v>
       </c>
       <c r="BD106" s="31">
-        <f>AD106*AQ106</f>
+        <f>IF(E106="cancelled",0,AD106*AQ106)</f>
         <v>0</v>
       </c>
       <c r="BE106" s="31">
@@ -39944,7 +39944,7 @@
         <v>0</v>
       </c>
       <c r="BJ106" s="31">
-        <f>AD106*AR106</f>
+        <f>IF(E106="cancelled",0,AD106*AR106)</f>
         <v>0</v>
       </c>
       <c r="BK106" s="31">
@@ -40118,7 +40118,7 @@
         <v>8964553</v>
       </c>
       <c r="AN107" s="9">
-        <f>AD107*T107</f>
+        <f>IF(E107="cancelled",0,AD107*T107)</f>
         <v>5</v>
       </c>
       <c r="AO107" s="9">
@@ -40158,7 +40158,7 @@
         <v>2109306.6</v>
       </c>
       <c r="AX107" s="31">
-        <f>AD107*AP107</f>
+        <f>IF(E107="cancelled",0,AD107*AP107)</f>
         <v>5</v>
       </c>
       <c r="AY107" s="31">
@@ -40182,7 +40182,7 @@
         <v>2109306.6</v>
       </c>
       <c r="BD107" s="31">
-        <f>AD107*AQ107</f>
+        <f>IF(E107="cancelled",0,AD107*AQ107)</f>
         <v>5</v>
       </c>
       <c r="BE107" s="31">
@@ -40206,7 +40206,7 @@
         <v>0</v>
       </c>
       <c r="BJ107" s="31">
-        <f>AD107*AR107</f>
+        <f>IF(E107="cancelled",0,AD107*AR107)</f>
         <v>0</v>
       </c>
       <c r="BK107" s="31">
@@ -40380,7 +40380,7 @@
         <v>0</v>
       </c>
       <c r="AN108" s="9">
-        <f>AD108*T108</f>
+        <f>IF(E108="cancelled",0,AD108*T108)</f>
         <v>8</v>
       </c>
       <c r="AO108" s="9">
@@ -40420,7 +40420,7 @@
         <v>1291950.1900000002</v>
       </c>
       <c r="AX108" s="31">
-        <f>AD108*AP108</f>
+        <f>IF(E108="cancelled",0,AD108*AP108)</f>
         <v>8</v>
       </c>
       <c r="AY108" s="31">
@@ -40444,7 +40444,7 @@
         <v>1291950.1900000002</v>
       </c>
       <c r="BD108" s="31">
-        <f>AD108*AQ108</f>
+        <f>IF(E108="cancelled",0,AD108*AQ108)</f>
         <v>8</v>
       </c>
       <c r="BE108" s="31">
@@ -40468,7 +40468,7 @@
         <v>1291950.1900000002</v>
       </c>
       <c r="BJ108" s="31">
-        <f>AD108*AR108</f>
+        <f>IF(E108="cancelled",0,AD108*AR108)</f>
         <v>8</v>
       </c>
       <c r="BK108" s="31">
@@ -40642,7 +40642,7 @@
         <v>4286321</v>
       </c>
       <c r="AN109" s="9">
-        <f>AD109*T109</f>
+        <f>IF(E109="cancelled",0,AD109*T109)</f>
         <v>5</v>
       </c>
       <c r="AO109" s="9">
@@ -40682,7 +40682,7 @@
         <v>1008546.2000000001</v>
       </c>
       <c r="AX109" s="31">
-        <f>AD109*AP109</f>
+        <f>IF(E109="cancelled",0,AD109*AP109)</f>
         <v>5</v>
       </c>
       <c r="AY109" s="31">
@@ -40706,7 +40706,7 @@
         <v>1008546.2000000001</v>
       </c>
       <c r="BD109" s="31">
-        <f>AD109*AQ109</f>
+        <f>IF(E109="cancelled",0,AD109*AQ109)</f>
         <v>5</v>
       </c>
       <c r="BE109" s="31">
@@ -40730,7 +40730,7 @@
         <v>1008546.2000000001</v>
       </c>
       <c r="BJ109" s="31">
-        <f>AD109*AR109</f>
+        <f>IF(E109="cancelled",0,AD109*AR109)</f>
         <v>5</v>
       </c>
       <c r="BK109" s="31">
@@ -40904,7 +40904,7 @@
         <v>0</v>
       </c>
       <c r="AN110" s="9">
-        <f>AD110*T110</f>
+        <f>IF(E110="cancelled",0,AD110*T110)</f>
         <v>5</v>
       </c>
       <c r="AO110" s="9">
@@ -40944,7 +40944,7 @@
         <v>862593.9400000001</v>
       </c>
       <c r="AX110" s="31">
-        <f>AD110*AP110</f>
+        <f>IF(E110="cancelled",0,AD110*AP110)</f>
         <v>5</v>
       </c>
       <c r="AY110" s="31">
@@ -40968,7 +40968,7 @@
         <v>862593.9400000001</v>
       </c>
       <c r="BD110" s="31">
-        <f>AD110*AQ110</f>
+        <f>IF(E110="cancelled",0,AD110*AQ110)</f>
         <v>5</v>
       </c>
       <c r="BE110" s="31">
@@ -40992,7 +40992,7 @@
         <v>862593.9400000001</v>
       </c>
       <c r="BJ110" s="31">
-        <f>AD110*AR110</f>
+        <f>IF(E110="cancelled",0,AD110*AR110)</f>
         <v>5</v>
       </c>
       <c r="BK110" s="31">
@@ -41166,7 +41166,7 @@
         <v>7312184</v>
       </c>
       <c r="AN111" s="9">
-        <f>AD111*T111</f>
+        <f>IF(E111="cancelled",0,AD111*T111)</f>
         <v>2</v>
       </c>
       <c r="AO111" s="9">
@@ -41206,7 +41206,7 @@
         <v>1412581</v>
       </c>
       <c r="AX111" s="31">
-        <f>AD111*AP111</f>
+        <f>IF(E111="cancelled",0,AD111*AP111)</f>
         <v>2</v>
       </c>
       <c r="AY111" s="31">
@@ -41230,7 +41230,7 @@
         <v>1412581</v>
       </c>
       <c r="BD111" s="31">
-        <f>AD111*AQ111</f>
+        <f>IF(E111="cancelled",0,AD111*AQ111)</f>
         <v>2</v>
       </c>
       <c r="BE111" s="31">
@@ -41254,7 +41254,7 @@
         <v>1412581</v>
       </c>
       <c r="BJ111" s="31">
-        <f>AD111*AR111</f>
+        <f>IF(E111="cancelled",0,AD111*AR111)</f>
         <v>2</v>
       </c>
       <c r="BK111" s="31">
@@ -41428,7 +41428,7 @@
         <v>0</v>
       </c>
       <c r="AN112" s="9">
-        <f>AD112*T112</f>
+        <f>IF(E112="cancelled",0,AD112*T112)</f>
         <v>4</v>
       </c>
       <c r="AO112" s="9">
@@ -41468,7 +41468,7 @@
         <v>1466469.4000000001</v>
       </c>
       <c r="AX112" s="31">
-        <f>AD112*AP112</f>
+        <f>IF(E112="cancelled",0,AD112*AP112)</f>
         <v>4</v>
       </c>
       <c r="AY112" s="31">
@@ -41492,7 +41492,7 @@
         <v>1466469.4000000001</v>
       </c>
       <c r="BD112" s="31">
-        <f>AD112*AQ112</f>
+        <f>IF(E112="cancelled",0,AD112*AQ112)</f>
         <v>4</v>
       </c>
       <c r="BE112" s="31">
@@ -41516,7 +41516,7 @@
         <v>1466469.4000000001</v>
       </c>
       <c r="BJ112" s="31">
-        <f>AD112*AR112</f>
+        <f>IF(E112="cancelled",0,AD112*AR112)</f>
         <v>4</v>
       </c>
       <c r="BK112" s="31">
@@ -41690,7 +41690,7 @@
         <v>2157045</v>
       </c>
       <c r="AN113" s="9">
-        <f>AD113*T113</f>
+        <f>IF(E113="cancelled",0,AD113*T113)</f>
         <v>3</v>
       </c>
       <c r="AO113" s="9">
@@ -41730,7 +41730,7 @@
         <v>519770</v>
       </c>
       <c r="AX113" s="31">
-        <f>AD113*AP113</f>
+        <f>IF(E113="cancelled",0,AD113*AP113)</f>
         <v>3</v>
       </c>
       <c r="AY113" s="31">
@@ -41754,7 +41754,7 @@
         <v>519770</v>
       </c>
       <c r="BD113" s="31">
-        <f>AD113*AQ113</f>
+        <f>IF(E113="cancelled",0,AD113*AQ113)</f>
         <v>3</v>
       </c>
       <c r="BE113" s="31">
@@ -41778,7 +41778,7 @@
         <v>0</v>
       </c>
       <c r="BJ113" s="31">
-        <f>AD113*AR113</f>
+        <f>IF(E113="cancelled",0,AD113*AR113)</f>
         <v>0</v>
       </c>
       <c r="BK113" s="31">
@@ -41952,7 +41952,7 @@
         <v>0</v>
       </c>
       <c r="AN114" s="9">
-        <f>AD114*T114</f>
+        <f>IF(E114="cancelled",0,AD114*T114)</f>
         <v>5</v>
       </c>
       <c r="AO114" s="9">
@@ -41992,7 +41992,7 @@
         <v>2748288.6</v>
       </c>
       <c r="AX114" s="31">
-        <f>AD114*AP114</f>
+        <f>IF(E114="cancelled",0,AD114*AP114)</f>
         <v>5</v>
       </c>
       <c r="AY114" s="31">
@@ -42016,7 +42016,7 @@
         <v>0</v>
       </c>
       <c r="BD114" s="31">
-        <f>AD114*AQ114</f>
+        <f>IF(E114="cancelled",0,AD114*AQ114)</f>
         <v>0</v>
       </c>
       <c r="BE114" s="31">
@@ -42040,7 +42040,7 @@
         <v>0</v>
       </c>
       <c r="BJ114" s="31">
-        <f>AD114*AR114</f>
+        <f>IF(E114="cancelled",0,AD114*AR114)</f>
         <v>0</v>
       </c>
       <c r="BK114" s="31">
@@ -42214,7 +42214,7 @@
         <v>10346813</v>
       </c>
       <c r="AN115" s="9">
-        <f>AD115*T115</f>
+        <f>IF(E115="cancelled",0,AD115*T115)</f>
         <v>2</v>
       </c>
       <c r="AO115" s="9">
@@ -42254,7 +42254,7 @@
         <v>2119226.8000000003</v>
       </c>
       <c r="AX115" s="31">
-        <f>AD115*AP115</f>
+        <f>IF(E115="cancelled",0,AD115*AP115)</f>
         <v>2</v>
       </c>
       <c r="AY115" s="31">
@@ -42278,7 +42278,7 @@
         <v>2119226.8000000003</v>
       </c>
       <c r="BD115" s="31">
-        <f>AD115*AQ115</f>
+        <f>IF(E115="cancelled",0,AD115*AQ115)</f>
         <v>2</v>
       </c>
       <c r="BE115" s="31">
@@ -42302,7 +42302,7 @@
         <v>2119226.8000000003</v>
       </c>
       <c r="BJ115" s="31">
-        <f>AD115*AR115</f>
+        <f>IF(E115="cancelled",0,AD115*AR115)</f>
         <v>2</v>
       </c>
       <c r="BK115" s="31">
@@ -42476,7 +42476,7 @@
         <v>0</v>
       </c>
       <c r="AN116" s="9">
-        <f>AD116*T116</f>
+        <f>IF(E116="cancelled",0,AD116*T116)</f>
         <v>3</v>
       </c>
       <c r="AO116" s="9">
@@ -42516,7 +42516,7 @@
         <v>2536402.21</v>
       </c>
       <c r="AX116" s="31">
-        <f>AD116*AP116</f>
+        <f>IF(E116="cancelled",0,AD116*AP116)</f>
         <v>3</v>
       </c>
       <c r="AY116" s="31">
@@ -42540,7 +42540,7 @@
         <v>0</v>
       </c>
       <c r="BD116" s="31">
-        <f>AD116*AQ116</f>
+        <f>IF(E116="cancelled",0,AD116*AQ116)</f>
         <v>0</v>
       </c>
       <c r="BE116" s="31">
@@ -42564,7 +42564,7 @@
         <v>0</v>
       </c>
       <c r="BJ116" s="31">
-        <f>AD116*AR116</f>
+        <f>IF(E116="cancelled",0,AD116*AR116)</f>
         <v>0</v>
       </c>
       <c r="BK116" s="31">
@@ -42738,7 +42738,7 @@
         <v>7731286</v>
       </c>
       <c r="AN117" s="9">
-        <f>AD117*T117</f>
+        <f>IF(E117="cancelled",0,AD117*T117)</f>
         <v>3</v>
       </c>
       <c r="AO117" s="9">
@@ -42778,7 +42778,7 @@
         <v>1862960.6</v>
       </c>
       <c r="AX117" s="31">
-        <f>AD117*AP117</f>
+        <f>IF(E117="cancelled",0,AD117*AP117)</f>
         <v>3</v>
       </c>
       <c r="AY117" s="31">
@@ -42802,7 +42802,7 @@
         <v>1862960.6</v>
       </c>
       <c r="BD117" s="31">
-        <f>AD117*AQ117</f>
+        <f>IF(E117="cancelled",0,AD117*AQ117)</f>
         <v>3</v>
       </c>
       <c r="BE117" s="31">
@@ -42826,7 +42826,7 @@
         <v>0</v>
       </c>
       <c r="BJ117" s="31">
-        <f>AD117*AR117</f>
+        <f>IF(E117="cancelled",0,AD117*AR117)</f>
         <v>0</v>
       </c>
       <c r="BK117" s="31">
@@ -43000,7 +43000,7 @@
         <v>0</v>
       </c>
       <c r="AN118" s="9">
-        <f>AD118*T118</f>
+        <f>IF(E118="cancelled",0,AD118*T118)</f>
         <v>2</v>
       </c>
       <c r="AO118" s="9">
@@ -43040,7 +43040,7 @@
         <v>475312.52</v>
       </c>
       <c r="AX118" s="31">
-        <f>AD118*AP118</f>
+        <f>IF(E118="cancelled",0,AD118*AP118)</f>
         <v>2</v>
       </c>
       <c r="AY118" s="31">
@@ -43064,7 +43064,7 @@
         <v>0</v>
       </c>
       <c r="BD118" s="31">
-        <f>AD118*AQ118</f>
+        <f>IF(E118="cancelled",0,AD118*AQ118)</f>
         <v>0</v>
       </c>
       <c r="BE118" s="31">
@@ -43088,7 +43088,7 @@
         <v>0</v>
       </c>
       <c r="BJ118" s="31">
-        <f>AD118*AR118</f>
+        <f>IF(E118="cancelled",0,AD118*AR118)</f>
         <v>0</v>
       </c>
       <c r="BK118" s="31">
@@ -43262,7 +43262,7 @@
         <v>7947911</v>
       </c>
       <c r="AN119" s="9">
-        <f>AD119*T119</f>
+        <f>IF(E119="cancelled",0,AD119*T119)</f>
         <v>3</v>
       </c>
       <c r="AO119" s="9">
@@ -43302,7 +43302,7 @@
         <v>1870096.8</v>
       </c>
       <c r="AX119" s="31">
-        <f>AD119*AP119</f>
+        <f>IF(E119="cancelled",0,AD119*AP119)</f>
         <v>3</v>
       </c>
       <c r="AY119" s="31">
@@ -43326,7 +43326,7 @@
         <v>1870096.8</v>
       </c>
       <c r="BD119" s="31">
-        <f>AD119*AQ119</f>
+        <f>IF(E119="cancelled",0,AD119*AQ119)</f>
         <v>3</v>
       </c>
       <c r="BE119" s="31">
@@ -43350,7 +43350,7 @@
         <v>1870096.8</v>
       </c>
       <c r="BJ119" s="31">
-        <f>AD119*AR119</f>
+        <f>IF(E119="cancelled",0,AD119*AR119)</f>
         <v>3</v>
       </c>
       <c r="BK119" s="31">
@@ -43524,7 +43524,7 @@
         <v>0</v>
       </c>
       <c r="AN120" s="9">
-        <f>AD120*T120</f>
+        <f>IF(E120="cancelled",0,AD120*T120)</f>
         <v>7</v>
       </c>
       <c r="AO120" s="9">
@@ -43564,7 +43564,7 @@
         <v>1610196.1400000001</v>
       </c>
       <c r="AX120" s="31">
-        <f>AD120*AP120</f>
+        <f>IF(E120="cancelled",0,AD120*AP120)</f>
         <v>7</v>
       </c>
       <c r="AY120" s="31">
@@ -43588,7 +43588,7 @@
         <v>0</v>
       </c>
       <c r="BD120" s="31">
-        <f>AD120*AQ120</f>
+        <f>IF(E120="cancelled",0,AD120*AQ120)</f>
         <v>0</v>
       </c>
       <c r="BE120" s="31">
@@ -43612,7 +43612,7 @@
         <v>0</v>
       </c>
       <c r="BJ120" s="31">
-        <f>AD120*AR120</f>
+        <f>IF(E120="cancelled",0,AD120*AR120)</f>
         <v>0</v>
       </c>
       <c r="BK120" s="31">
@@ -43786,7 +43786,7 @@
         <v>2606422</v>
       </c>
       <c r="AN121" s="9">
-        <f>AD121*T121</f>
+        <f>IF(E121="cancelled",0,AD121*T121)</f>
         <v>5</v>
       </c>
       <c r="AO121" s="9">
@@ -43826,7 +43826,7 @@
         <v>521284.43000000005</v>
       </c>
       <c r="AX121" s="31">
-        <f>AD121*AP121</f>
+        <f>IF(E121="cancelled",0,AD121*AP121)</f>
         <v>5</v>
       </c>
       <c r="AY121" s="31">
@@ -43850,7 +43850,7 @@
         <v>521284.43000000005</v>
       </c>
       <c r="BD121" s="31">
-        <f>AD121*AQ121</f>
+        <f>IF(E121="cancelled",0,AD121*AQ121)</f>
         <v>5</v>
       </c>
       <c r="BE121" s="31">
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="BJ121" s="31">
-        <f>AD121*AR121</f>
+        <f>IF(E121="cancelled",0,AD121*AR121)</f>
         <v>0</v>
       </c>
       <c r="BK121" s="31">
@@ -44048,7 +44048,7 @@
         <v>0</v>
       </c>
       <c r="AN122" s="9">
-        <f>AD122*T122</f>
+        <f>IF(E122="cancelled",0,AD122*T122)</f>
         <v>4</v>
       </c>
       <c r="AO122" s="9">
@@ -44088,7 +44088,7 @@
         <v>953649.68</v>
       </c>
       <c r="AX122" s="31">
-        <f>AD122*AP122</f>
+        <f>IF(E122="cancelled",0,AD122*AP122)</f>
         <v>4</v>
       </c>
       <c r="AY122" s="31">
@@ -44112,7 +44112,7 @@
         <v>0</v>
       </c>
       <c r="BD122" s="31">
-        <f>AD122*AQ122</f>
+        <f>IF(E122="cancelled",0,AD122*AQ122)</f>
         <v>0</v>
       </c>
       <c r="BE122" s="31">
@@ -44136,7 +44136,7 @@
         <v>0</v>
       </c>
       <c r="BJ122" s="31">
-        <f>AD122*AR122</f>
+        <f>IF(E122="cancelled",0,AD122*AR122)</f>
         <v>0</v>
       </c>
       <c r="BK122" s="31">
@@ -44310,7 +44310,7 @@
         <v>2609288</v>
       </c>
       <c r="AN123" s="9">
-        <f>AD123*T123</f>
+        <f>IF(E123="cancelled",0,AD123*T123)</f>
         <v>3</v>
       </c>
       <c r="AO123" s="9">
@@ -44350,7 +44350,7 @@
         <v>613950</v>
       </c>
       <c r="AX123" s="31">
-        <f>AD123*AP123</f>
+        <f>IF(E123="cancelled",0,AD123*AP123)</f>
         <v>3</v>
       </c>
       <c r="AY123" s="31">
@@ -44374,7 +44374,7 @@
         <v>613950</v>
       </c>
       <c r="BD123" s="31">
-        <f>AD123*AQ123</f>
+        <f>IF(E123="cancelled",0,AD123*AQ123)</f>
         <v>3</v>
       </c>
       <c r="BE123" s="31">
@@ -44398,7 +44398,7 @@
         <v>0</v>
       </c>
       <c r="BJ123" s="31">
-        <f>AD123*AR123</f>
+        <f>IF(E123="cancelled",0,AD123*AR123)</f>
         <v>0</v>
       </c>
       <c r="BK123" s="31">
@@ -44572,7 +44572,7 @@
         <v>0</v>
       </c>
       <c r="AN124" s="9">
-        <f>AD124*T124</f>
+        <f>IF(E124="cancelled",0,AD124*T124)</f>
         <v>5</v>
       </c>
       <c r="AO124" s="9">
@@ -44612,7 +44612,7 @@
         <v>2427920.62</v>
       </c>
       <c r="AX124" s="31">
-        <f>AD124*AP124</f>
+        <f>IF(E124="cancelled",0,AD124*AP124)</f>
         <v>5</v>
       </c>
       <c r="AY124" s="31">
@@ -44636,7 +44636,7 @@
         <v>2427920.62</v>
       </c>
       <c r="BD124" s="31">
-        <f>AD124*AQ124</f>
+        <f>IF(E124="cancelled",0,AD124*AQ124)</f>
         <v>5</v>
       </c>
       <c r="BE124" s="31">
@@ -44660,7 +44660,7 @@
         <v>2427920.62</v>
       </c>
       <c r="BJ124" s="31">
-        <f>AD124*AR124</f>
+        <f>IF(E124="cancelled",0,AD124*AR124)</f>
         <v>5</v>
       </c>
       <c r="BK124" s="31">
@@ -44834,7 +44834,7 @@
         <v>10661797</v>
       </c>
       <c r="AN125" s="9">
-        <f>AD125*T125</f>
+        <f>IF(E125="cancelled",0,AD125*T125)</f>
         <v>6</v>
       </c>
       <c r="AO125" s="9">
@@ -44874,7 +44874,7 @@
         <v>2508658.2</v>
       </c>
       <c r="AX125" s="31">
-        <f>AD125*AP125</f>
+        <f>IF(E125="cancelled",0,AD125*AP125)</f>
         <v>6</v>
       </c>
       <c r="AY125" s="31">
@@ -44898,7 +44898,7 @@
         <v>2508658.2</v>
       </c>
       <c r="BD125" s="31">
-        <f>AD125*AQ125</f>
+        <f>IF(E125="cancelled",0,AD125*AQ125)</f>
         <v>6</v>
       </c>
       <c r="BE125" s="31">
@@ -44922,7 +44922,7 @@
         <v>0</v>
       </c>
       <c r="BJ125" s="31">
-        <f>AD125*AR125</f>
+        <f>IF(E125="cancelled",0,AD125*AR125)</f>
         <v>0</v>
       </c>
       <c r="BK125" s="31">
@@ -45096,7 +45096,7 @@
         <v>0</v>
       </c>
       <c r="AN126" s="9">
-        <f>AD126*T126</f>
+        <f>IF(E126="cancelled",0,AD126*T126)</f>
         <v>3</v>
       </c>
       <c r="AO126" s="9">
@@ -45136,7 +45136,7 @@
         <v>2338131.72</v>
       </c>
       <c r="AX126" s="31">
-        <f>AD126*AP126</f>
+        <f>IF(E126="cancelled",0,AD126*AP126)</f>
         <v>3</v>
       </c>
       <c r="AY126" s="31">
@@ -45160,7 +45160,7 @@
         <v>2338131.72</v>
       </c>
       <c r="BD126" s="31">
-        <f>AD126*AQ126</f>
+        <f>IF(E126="cancelled",0,AD126*AQ126)</f>
         <v>3</v>
       </c>
       <c r="BE126" s="31">
@@ -45184,7 +45184,7 @@
         <v>2338131.72</v>
       </c>
       <c r="BJ126" s="31">
-        <f>AD126*AR126</f>
+        <f>IF(E126="cancelled",0,AD126*AR126)</f>
         <v>3</v>
       </c>
       <c r="BK126" s="31">
@@ -45358,7 +45358,7 @@
         <v>8565368</v>
       </c>
       <c r="AN127" s="9">
-        <f>AD127*T127</f>
+        <f>IF(E127="cancelled",0,AD127*T127)</f>
         <v>5</v>
       </c>
       <c r="AO127" s="9">
@@ -45398,7 +45398,7 @@
         <v>1654673.4100000001</v>
       </c>
       <c r="AX127" s="31">
-        <f>AD127*AP127</f>
+        <f>IF(E127="cancelled",0,AD127*AP127)</f>
         <v>5</v>
       </c>
       <c r="AY127" s="31">
@@ -45422,7 +45422,7 @@
         <v>1654673.4100000001</v>
       </c>
       <c r="BD127" s="31">
-        <f>AD127*AQ127</f>
+        <f>IF(E127="cancelled",0,AD127*AQ127)</f>
         <v>5</v>
       </c>
       <c r="BE127" s="31">
@@ -45446,7 +45446,7 @@
         <v>0</v>
       </c>
       <c r="BJ127" s="31">
-        <f>AD127*AR127</f>
+        <f>IF(E127="cancelled",0,AD127*AR127)</f>
         <v>0</v>
       </c>
       <c r="BK127" s="31">
@@ -45620,7 +45620,7 @@
         <v>0</v>
       </c>
       <c r="AN128" s="9">
-        <f>AD128*T128</f>
+        <f>IF(E128="cancelled",0,AD128*T128)</f>
         <v>5</v>
       </c>
       <c r="AO128" s="9">
@@ -45660,7 +45660,7 @@
         <v>2194275.6</v>
       </c>
       <c r="AX128" s="31">
-        <f>AD128*AP128</f>
+        <f>IF(E128="cancelled",0,AD128*AP128)</f>
         <v>5</v>
       </c>
       <c r="AY128" s="31">
@@ -45684,7 +45684,7 @@
         <v>0</v>
       </c>
       <c r="BD128" s="31">
-        <f>AD128*AQ128</f>
+        <f>IF(E128="cancelled",0,AD128*AQ128)</f>
         <v>0</v>
       </c>
       <c r="BE128" s="31">
@@ -45708,7 +45708,7 @@
         <v>0</v>
       </c>
       <c r="BJ128" s="31">
-        <f>AD128*AR128</f>
+        <f>IF(E128="cancelled",0,AD128*AR128)</f>
         <v>0</v>
       </c>
       <c r="BK128" s="31">
@@ -45882,7 +45882,7 @@
         <v>6745121</v>
       </c>
       <c r="AN129" s="9">
-        <f>AD129*T129</f>
+        <f>IF(E129="cancelled",0,AD129*T129)</f>
         <v>3</v>
       </c>
       <c r="AO129" s="9">
@@ -45922,7 +45922,7 @@
         <v>1303034.7000000002</v>
       </c>
       <c r="AX129" s="31">
-        <f>AD129*AP129</f>
+        <f>IF(E129="cancelled",0,AD129*AP129)</f>
         <v>3</v>
       </c>
       <c r="AY129" s="31">
@@ -45946,7 +45946,7 @@
         <v>1303034.7000000002</v>
       </c>
       <c r="BD129" s="31">
-        <f>AD129*AQ129</f>
+        <f>IF(E129="cancelled",0,AD129*AQ129)</f>
         <v>3</v>
       </c>
       <c r="BE129" s="31">
@@ -45970,7 +45970,7 @@
         <v>0</v>
       </c>
       <c r="BJ129" s="31">
-        <f>AD129*AR129</f>
+        <f>IF(E129="cancelled",0,AD129*AR129)</f>
         <v>0</v>
       </c>
       <c r="BK129" s="31">
@@ -46144,7 +46144,7 @@
         <v>0</v>
       </c>
       <c r="AN130" s="9">
-        <f>AD130*T130</f>
+        <f>IF(E130="cancelled",0,AD130*T130)</f>
         <v>4</v>
       </c>
       <c r="AO130" s="9">
@@ -46184,7 +46184,7 @@
         <v>2312485.69</v>
       </c>
       <c r="AX130" s="31">
-        <f>AD130*AP130</f>
+        <f>IF(E130="cancelled",0,AD130*AP130)</f>
         <v>4</v>
       </c>
       <c r="AY130" s="31">
@@ -46208,7 +46208,7 @@
         <v>0</v>
       </c>
       <c r="BD130" s="31">
-        <f>AD130*AQ130</f>
+        <f>IF(E130="cancelled",0,AD130*AQ130)</f>
         <v>0</v>
       </c>
       <c r="BE130" s="31">
@@ -46232,7 +46232,7 @@
         <v>0</v>
       </c>
       <c r="BJ130" s="31">
-        <f>AD130*AR130</f>
+        <f>IF(E130="cancelled",0,AD130*AR130)</f>
         <v>0</v>
       </c>
       <c r="BK130" s="31">
@@ -46406,7 +46406,7 @@
         <v>10593600</v>
       </c>
       <c r="AN131" s="9">
-        <f>AD131*T131</f>
+        <f>IF(E131="cancelled",0,AD131*T131)</f>
         <v>2</v>
       </c>
       <c r="AO131" s="9">
@@ -46446,7 +46446,7 @@
         <v>2492611.8000000003</v>
       </c>
       <c r="AX131" s="31">
-        <f>AD131*AP131</f>
+        <f>IF(E131="cancelled",0,AD131*AP131)</f>
         <v>2</v>
       </c>
       <c r="AY131" s="31">
@@ -46470,7 +46470,7 @@
         <v>2492611.8000000003</v>
       </c>
       <c r="BD131" s="31">
-        <f>AD131*AQ131</f>
+        <f>IF(E131="cancelled",0,AD131*AQ131)</f>
         <v>2</v>
       </c>
       <c r="BE131" s="31">
@@ -46494,7 +46494,7 @@
         <v>0</v>
       </c>
       <c r="BJ131" s="31">
-        <f>AD131*AR131</f>
+        <f>IF(E131="cancelled",0,AD131*AR131)</f>
         <v>0</v>
       </c>
       <c r="BK131" s="31">
@@ -46668,8 +46668,8 @@
         <v>0</v>
       </c>
       <c r="AN132" s="9">
-        <f>AD132*T132</f>
-        <v>8</v>
+        <f>IF(E132="cancelled",0,AD132*T132)</f>
+        <v>0</v>
       </c>
       <c r="AO132" s="9">
         <f>S132*AK132</f>
@@ -46708,8 +46708,8 @@
         <v>0</v>
       </c>
       <c r="AX132" s="31">
-        <f>AD132*AP132</f>
-        <v>8</v>
+        <f>IF(E132="cancelled",0,AD132*AP132)</f>
+        <v>0</v>
       </c>
       <c r="AY132" s="31">
         <f>IF(AND(AP132=1,AD132&gt;0),1,0)</f>
@@ -46732,8 +46732,8 @@
         <v>0</v>
       </c>
       <c r="BD132" s="31">
-        <f>AD132*AQ132</f>
-        <v>8</v>
+        <f>IF(E132="cancelled",0,AD132*AQ132)</f>
+        <v>0</v>
       </c>
       <c r="BE132" s="31">
         <f>IF(AND(AQ132=1,AD132&gt;0),1,0)</f>
@@ -46756,8 +46756,8 @@
         <v>0</v>
       </c>
       <c r="BJ132" s="31">
-        <f>AD132*AR132</f>
-        <v>8</v>
+        <f>IF(E132="cancelled",0,AD132*AR132)</f>
+        <v>0</v>
       </c>
       <c r="BK132" s="31">
         <f>IF(AND(AR132=1,AD132&gt;0),1,0)</f>
@@ -46930,8 +46930,8 @@
         <v>0</v>
       </c>
       <c r="AN133" s="9">
-        <f>AD133*T133</f>
-        <v>3</v>
+        <f>IF(E133="cancelled",0,AD133*T133)</f>
+        <v>0</v>
       </c>
       <c r="AO133" s="9">
         <f>S133*AK133</f>
@@ -46970,8 +46970,8 @@
         <v>0</v>
       </c>
       <c r="AX133" s="31">
-        <f>AD133*AP133</f>
-        <v>3</v>
+        <f>IF(E133="cancelled",0,AD133*AP133)</f>
+        <v>0</v>
       </c>
       <c r="AY133" s="31">
         <f>IF(AND(AP133=1,AD133&gt;0),1,0)</f>
@@ -46994,8 +46994,8 @@
         <v>0</v>
       </c>
       <c r="BD133" s="31">
-        <f>AD133*AQ133</f>
-        <v>3</v>
+        <f>IF(E133="cancelled",0,AD133*AQ133)</f>
+        <v>0</v>
       </c>
       <c r="BE133" s="31">
         <f>IF(AND(AQ133=1,AD133&gt;0),1,0)</f>
@@ -47018,8 +47018,8 @@
         <v>0</v>
       </c>
       <c r="BJ133" s="31">
-        <f>AD133*AR133</f>
-        <v>3</v>
+        <f>IF(E133="cancelled",0,AD133*AR133)</f>
+        <v>0</v>
       </c>
       <c r="BK133" s="31">
         <f>IF(AND(AR133=1,AD133&gt;0),1,0)</f>
@@ -47192,8 +47192,8 @@
         <v>0</v>
       </c>
       <c r="AN134" s="9">
-        <f>AD134*T134</f>
-        <v>2</v>
+        <f>IF(E134="cancelled",0,AD134*T134)</f>
+        <v>0</v>
       </c>
       <c r="AO134" s="9">
         <f>S134*AK134</f>
@@ -47232,8 +47232,8 @@
         <v>0</v>
       </c>
       <c r="AX134" s="31">
-        <f>AD134*AP134</f>
-        <v>2</v>
+        <f>IF(E134="cancelled",0,AD134*AP134)</f>
+        <v>0</v>
       </c>
       <c r="AY134" s="31">
         <f>IF(AND(AP134=1,AD134&gt;0),1,0)</f>
@@ -47256,8 +47256,8 @@
         <v>0</v>
       </c>
       <c r="BD134" s="31">
-        <f>AD134*AQ134</f>
-        <v>2</v>
+        <f>IF(E134="cancelled",0,AD134*AQ134)</f>
+        <v>0</v>
       </c>
       <c r="BE134" s="31">
         <f>IF(AND(AQ134=1,AD134&gt;0),1,0)</f>
@@ -47280,8 +47280,8 @@
         <v>0</v>
       </c>
       <c r="BJ134" s="31">
-        <f>AD134*AR134</f>
-        <v>2</v>
+        <f>IF(E134="cancelled",0,AD134*AR134)</f>
+        <v>0</v>
       </c>
       <c r="BK134" s="31">
         <f>IF(AND(AR134=1,AD134&gt;0),1,0)</f>
@@ -47454,8 +47454,8 @@
         <v>0</v>
       </c>
       <c r="AN135" s="9">
-        <f>AD135*T135</f>
-        <v>8</v>
+        <f>IF(E135="cancelled",0,AD135*T135)</f>
+        <v>0</v>
       </c>
       <c r="AO135" s="9">
         <f>S135*AK135</f>
@@ -47494,8 +47494,8 @@
         <v>0</v>
       </c>
       <c r="AX135" s="31">
-        <f>AD135*AP135</f>
-        <v>8</v>
+        <f>IF(E135="cancelled",0,AD135*AP135)</f>
+        <v>0</v>
       </c>
       <c r="AY135" s="31">
         <f>IF(AND(AP135=1,AD135&gt;0),1,0)</f>
@@ -47518,8 +47518,8 @@
         <v>0</v>
       </c>
       <c r="BD135" s="31">
-        <f>AD135*AQ135</f>
-        <v>8</v>
+        <f>IF(E135="cancelled",0,AD135*AQ135)</f>
+        <v>0</v>
       </c>
       <c r="BE135" s="31">
         <f>IF(AND(AQ135=1,AD135&gt;0),1,0)</f>
@@ -47542,8 +47542,8 @@
         <v>0</v>
       </c>
       <c r="BJ135" s="31">
-        <f>AD135*AR135</f>
-        <v>8</v>
+        <f>IF(E135="cancelled",0,AD135*AR135)</f>
+        <v>0</v>
       </c>
       <c r="BK135" s="31">
         <f>IF(AND(AR135=1,AD135&gt;0),1,0)</f>
@@ -47716,8 +47716,8 @@
         <v>0</v>
       </c>
       <c r="AN136" s="9">
-        <f>AD136*T136</f>
-        <v>2</v>
+        <f>IF(E136="cancelled",0,AD136*T136)</f>
+        <v>0</v>
       </c>
       <c r="AO136" s="9">
         <f>S136*AK136</f>
@@ -47756,8 +47756,8 @@
         <v>0</v>
       </c>
       <c r="AX136" s="31">
-        <f>AD136*AP136</f>
-        <v>2</v>
+        <f>IF(E136="cancelled",0,AD136*AP136)</f>
+        <v>0</v>
       </c>
       <c r="AY136" s="31">
         <f>IF(AND(AP136=1,AD136&gt;0),1,0)</f>
@@ -47780,8 +47780,8 @@
         <v>0</v>
       </c>
       <c r="BD136" s="31">
-        <f>AD136*AQ136</f>
-        <v>2</v>
+        <f>IF(E136="cancelled",0,AD136*AQ136)</f>
+        <v>0</v>
       </c>
       <c r="BE136" s="31">
         <f>IF(AND(AQ136=1,AD136&gt;0),1,0)</f>
@@ -47804,8 +47804,8 @@
         <v>0</v>
       </c>
       <c r="BJ136" s="31">
-        <f>AD136*AR136</f>
-        <v>2</v>
+        <f>IF(E136="cancelled",0,AD136*AR136)</f>
+        <v>0</v>
       </c>
       <c r="BK136" s="31">
         <f>IF(AND(AR136=1,AD136&gt;0),1,0)</f>
@@ -47978,8 +47978,8 @@
         <v>0</v>
       </c>
       <c r="AN137" s="9">
-        <f>AD137*T137</f>
-        <v>7</v>
+        <f>IF(E137="cancelled",0,AD137*T137)</f>
+        <v>0</v>
       </c>
       <c r="AO137" s="9">
         <f>S137*AK137</f>
@@ -48018,8 +48018,8 @@
         <v>0</v>
       </c>
       <c r="AX137" s="31">
-        <f>AD137*AP137</f>
-        <v>7</v>
+        <f>IF(E137="cancelled",0,AD137*AP137)</f>
+        <v>0</v>
       </c>
       <c r="AY137" s="31">
         <f>IF(AND(AP137=1,AD137&gt;0),1,0)</f>
@@ -48042,8 +48042,8 @@
         <v>0</v>
       </c>
       <c r="BD137" s="31">
-        <f>AD137*AQ137</f>
-        <v>7</v>
+        <f>IF(E137="cancelled",0,AD137*AQ137)</f>
+        <v>0</v>
       </c>
       <c r="BE137" s="31">
         <f>IF(AND(AQ137=1,AD137&gt;0),1,0)</f>
@@ -48066,8 +48066,8 @@
         <v>0</v>
       </c>
       <c r="BJ137" s="31">
-        <f>AD137*AR137</f>
-        <v>7</v>
+        <f>IF(E137="cancelled",0,AD137*AR137)</f>
+        <v>0</v>
       </c>
       <c r="BK137" s="31">
         <f>IF(AND(AR137=1,AD137&gt;0),1,0)</f>
@@ -48240,8 +48240,8 @@
         <v>0</v>
       </c>
       <c r="AN138" s="9">
-        <f>AD138*T138</f>
-        <v>5</v>
+        <f>IF(E138="cancelled",0,AD138*T138)</f>
+        <v>0</v>
       </c>
       <c r="AO138" s="9">
         <f>S138*AK138</f>
@@ -48280,8 +48280,8 @@
         <v>0</v>
       </c>
       <c r="AX138" s="31">
-        <f>AD138*AP138</f>
-        <v>5</v>
+        <f>IF(E138="cancelled",0,AD138*AP138)</f>
+        <v>0</v>
       </c>
       <c r="AY138" s="31">
         <f>IF(AND(AP138=1,AD138&gt;0),1,0)</f>
@@ -48304,8 +48304,8 @@
         <v>0</v>
       </c>
       <c r="BD138" s="31">
-        <f>AD138*AQ138</f>
-        <v>5</v>
+        <f>IF(E138="cancelled",0,AD138*AQ138)</f>
+        <v>0</v>
       </c>
       <c r="BE138" s="31">
         <f>IF(AND(AQ138=1,AD138&gt;0),1,0)</f>
@@ -48328,8 +48328,8 @@
         <v>0</v>
       </c>
       <c r="BJ138" s="31">
-        <f>AD138*AR138</f>
-        <v>5</v>
+        <f>IF(E138="cancelled",0,AD138*AR138)</f>
+        <v>0</v>
       </c>
       <c r="BK138" s="31">
         <f>IF(AND(AR138=1,AD138&gt;0),1,0)</f>
@@ -48502,8 +48502,8 @@
         <v>0</v>
       </c>
       <c r="AN139" s="9">
-        <f>AD139*T139</f>
-        <v>7</v>
+        <f>IF(E139="cancelled",0,AD139*T139)</f>
+        <v>0</v>
       </c>
       <c r="AO139" s="9">
         <f>S139*AK139</f>
@@ -48542,8 +48542,8 @@
         <v>0</v>
       </c>
       <c r="AX139" s="31">
-        <f>AD139*AP139</f>
-        <v>7</v>
+        <f>IF(E139="cancelled",0,AD139*AP139)</f>
+        <v>0</v>
       </c>
       <c r="AY139" s="31">
         <f>IF(AND(AP139=1,AD139&gt;0),1,0)</f>
@@ -48566,8 +48566,8 @@
         <v>0</v>
       </c>
       <c r="BD139" s="31">
-        <f>AD139*AQ139</f>
-        <v>7</v>
+        <f>IF(E139="cancelled",0,AD139*AQ139)</f>
+        <v>0</v>
       </c>
       <c r="BE139" s="31">
         <f>IF(AND(AQ139=1,AD139&gt;0),1,0)</f>
@@ -48590,8 +48590,8 @@
         <v>0</v>
       </c>
       <c r="BJ139" s="31">
-        <f>AD139*AR139</f>
-        <v>7</v>
+        <f>IF(E139="cancelled",0,AD139*AR139)</f>
+        <v>0</v>
       </c>
       <c r="BK139" s="31">
         <f>IF(AND(AR139=1,AD139&gt;0),1,0)</f>
@@ -48764,8 +48764,8 @@
         <v>0</v>
       </c>
       <c r="AN140" s="9">
-        <f>AD140*T140</f>
-        <v>3</v>
+        <f>IF(E140="cancelled",0,AD140*T140)</f>
+        <v>0</v>
       </c>
       <c r="AO140" s="9">
         <f>S140*AK140</f>
@@ -48804,8 +48804,8 @@
         <v>0</v>
       </c>
       <c r="AX140" s="31">
-        <f>AD140*AP140</f>
-        <v>3</v>
+        <f>IF(E140="cancelled",0,AD140*AP140)</f>
+        <v>0</v>
       </c>
       <c r="AY140" s="31">
         <f>IF(AND(AP140=1,AD140&gt;0),1,0)</f>
@@ -48828,8 +48828,8 @@
         <v>0</v>
       </c>
       <c r="BD140" s="31">
-        <f>AD140*AQ140</f>
-        <v>3</v>
+        <f>IF(E140="cancelled",0,AD140*AQ140)</f>
+        <v>0</v>
       </c>
       <c r="BE140" s="31">
         <f>IF(AND(AQ140=1,AD140&gt;0),1,0)</f>
@@ -48852,8 +48852,8 @@
         <v>0</v>
       </c>
       <c r="BJ140" s="31">
-        <f>AD140*AR140</f>
-        <v>3</v>
+        <f>IF(E140="cancelled",0,AD140*AR140)</f>
+        <v>0</v>
       </c>
       <c r="BK140" s="31">
         <f>IF(AND(AR140=1,AD140&gt;0),1,0)</f>
@@ -49026,8 +49026,8 @@
         <v>0</v>
       </c>
       <c r="AN141" s="9">
-        <f>AD141*T141</f>
-        <v>8</v>
+        <f>IF(E141="cancelled",0,AD141*T141)</f>
+        <v>0</v>
       </c>
       <c r="AO141" s="9">
         <f>S141*AK141</f>
@@ -49066,8 +49066,8 @@
         <v>0</v>
       </c>
       <c r="AX141" s="31">
-        <f>AD141*AP141</f>
-        <v>8</v>
+        <f>IF(E141="cancelled",0,AD141*AP141)</f>
+        <v>0</v>
       </c>
       <c r="AY141" s="31">
         <f>IF(AND(AP141=1,AD141&gt;0),1,0)</f>
@@ -49090,8 +49090,8 @@
         <v>0</v>
       </c>
       <c r="BD141" s="31">
-        <f>AD141*AQ141</f>
-        <v>8</v>
+        <f>IF(E141="cancelled",0,AD141*AQ141)</f>
+        <v>0</v>
       </c>
       <c r="BE141" s="31">
         <f>IF(AND(AQ141=1,AD141&gt;0),1,0)</f>
@@ -49114,8 +49114,8 @@
         <v>0</v>
       </c>
       <c r="BJ141" s="31">
-        <f>AD141*AR141</f>
-        <v>8</v>
+        <f>IF(E141="cancelled",0,AD141*AR141)</f>
+        <v>0</v>
       </c>
       <c r="BK141" s="31">
         <f>IF(AND(AR141=1,AD141&gt;0),1,0)</f>
@@ -49288,8 +49288,8 @@
         <v>0</v>
       </c>
       <c r="AN142" s="9">
-        <f>AD142*T142</f>
-        <v>8</v>
+        <f>IF(E142="cancelled",0,AD142*T142)</f>
+        <v>0</v>
       </c>
       <c r="AO142" s="9">
         <f>S142*AK142</f>
@@ -49328,8 +49328,8 @@
         <v>0</v>
       </c>
       <c r="AX142" s="31">
-        <f>AD142*AP142</f>
-        <v>8</v>
+        <f>IF(E142="cancelled",0,AD142*AP142)</f>
+        <v>0</v>
       </c>
       <c r="AY142" s="31">
         <f>IF(AND(AP142=1,AD142&gt;0),1,0)</f>
@@ -49352,8 +49352,8 @@
         <v>0</v>
       </c>
       <c r="BD142" s="31">
-        <f>AD142*AQ142</f>
-        <v>8</v>
+        <f>IF(E142="cancelled",0,AD142*AQ142)</f>
+        <v>0</v>
       </c>
       <c r="BE142" s="31">
         <f>IF(AND(AQ142=1,AD142&gt;0),1,0)</f>
@@ -49376,8 +49376,8 @@
         <v>0</v>
       </c>
       <c r="BJ142" s="31">
-        <f>AD142*AR142</f>
-        <v>8</v>
+        <f>IF(E142="cancelled",0,AD142*AR142)</f>
+        <v>0</v>
       </c>
       <c r="BK142" s="31">
         <f>IF(AND(AR142=1,AD142&gt;0),1,0)</f>
@@ -49550,8 +49550,8 @@
         <v>0</v>
       </c>
       <c r="AN143" s="9">
-        <f>AD143*T143</f>
-        <v>2</v>
+        <f>IF(E143="cancelled",0,AD143*T143)</f>
+        <v>0</v>
       </c>
       <c r="AO143" s="9">
         <f>S143*AK143</f>
@@ -49590,8 +49590,8 @@
         <v>0</v>
       </c>
       <c r="AX143" s="31">
-        <f>AD143*AP143</f>
-        <v>2</v>
+        <f>IF(E143="cancelled",0,AD143*AP143)</f>
+        <v>0</v>
       </c>
       <c r="AY143" s="31">
         <f>IF(AND(AP143=1,AD143&gt;0),1,0)</f>
@@ -49614,8 +49614,8 @@
         <v>0</v>
       </c>
       <c r="BD143" s="31">
-        <f>AD143*AQ143</f>
-        <v>2</v>
+        <f>IF(E143="cancelled",0,AD143*AQ143)</f>
+        <v>0</v>
       </c>
       <c r="BE143" s="31">
         <f>IF(AND(AQ143=1,AD143&gt;0),1,0)</f>
@@ -49638,8 +49638,8 @@
         <v>0</v>
       </c>
       <c r="BJ143" s="31">
-        <f>AD143*AR143</f>
-        <v>2</v>
+        <f>IF(E143="cancelled",0,AD143*AR143)</f>
+        <v>0</v>
       </c>
       <c r="BK143" s="31">
         <f>IF(AND(AR143=1,AD143&gt;0),1,0)</f>
@@ -49812,7 +49812,7 @@
         <v>0</v>
       </c>
       <c r="AN144" s="9">
-        <f>AD144*T144</f>
+        <f>IF(E144="cancelled",0,AD144*T144)</f>
         <v>6</v>
       </c>
       <c r="AO144" s="9">
@@ -49852,7 +49852,7 @@
         <v>1182359.86</v>
       </c>
       <c r="AX144" s="31">
-        <f>AD144*AP144</f>
+        <f>IF(E144="cancelled",0,AD144*AP144)</f>
         <v>6</v>
       </c>
       <c r="AY144" s="31">
@@ -49876,7 +49876,7 @@
         <v>1182359.86</v>
       </c>
       <c r="BD144" s="31">
-        <f>AD144*AQ144</f>
+        <f>IF(E144="cancelled",0,AD144*AQ144)</f>
         <v>6</v>
       </c>
       <c r="BE144" s="31">
@@ -49900,7 +49900,7 @@
         <v>1182359.86</v>
       </c>
       <c r="BJ144" s="31">
-        <f>AD144*AR144</f>
+        <f>IF(E144="cancelled",0,AD144*AR144)</f>
         <v>6</v>
       </c>
       <c r="BK144" s="31">
@@ -50074,7 +50074,7 @@
         <v>7115398</v>
       </c>
       <c r="AN145" s="9">
-        <f>AD145*T145</f>
+        <f>IF(E145="cancelled",0,AD145*T145)</f>
         <v>3</v>
       </c>
       <c r="AO145" s="9">
@@ -50114,7 +50114,7 @@
         <v>1423079.6900000002</v>
       </c>
       <c r="AX145" s="31">
-        <f>AD145*AP145</f>
+        <f>IF(E145="cancelled",0,AD145*AP145)</f>
         <v>3</v>
       </c>
       <c r="AY145" s="31">
@@ -50138,7 +50138,7 @@
         <v>1423079.6900000002</v>
       </c>
       <c r="BD145" s="31">
-        <f>AD145*AQ145</f>
+        <f>IF(E145="cancelled",0,AD145*AQ145)</f>
         <v>3</v>
       </c>
       <c r="BE145" s="31">
@@ -50162,7 +50162,7 @@
         <v>1423079.6900000002</v>
       </c>
       <c r="BJ145" s="31">
-        <f>AD145*AR145</f>
+        <f>IF(E145="cancelled",0,AD145*AR145)</f>
         <v>3</v>
       </c>
       <c r="BK145" s="31">
@@ -50336,7 +50336,7 @@
         <v>0</v>
       </c>
       <c r="AN146" s="9">
-        <f>AD146*T146</f>
+        <f>IF(E146="cancelled",0,AD146*T146)</f>
         <v>5</v>
       </c>
       <c r="AO146" s="9">
@@ -50376,7 +50376,7 @@
         <v>1695621.1400000001</v>
       </c>
       <c r="AX146" s="31">
-        <f>AD146*AP146</f>
+        <f>IF(E146="cancelled",0,AD146*AP146)</f>
         <v>5</v>
       </c>
       <c r="AY146" s="31">
@@ -50400,7 +50400,7 @@
         <v>0</v>
       </c>
       <c r="BD146" s="31">
-        <f>AD146*AQ146</f>
+        <f>IF(E146="cancelled",0,AD146*AQ146)</f>
         <v>0</v>
       </c>
       <c r="BE146" s="31">
@@ -50424,7 +50424,7 @@
         <v>0</v>
       </c>
       <c r="BJ146" s="31">
-        <f>AD146*AR146</f>
+        <f>IF(E146="cancelled",0,AD146*AR146)</f>
         <v>0</v>
       </c>
       <c r="BK146" s="31">
@@ -50598,7 +50598,7 @@
         <v>2218910</v>
       </c>
       <c r="AN147" s="9">
-        <f>AD147*T147</f>
+        <f>IF(E147="cancelled",0,AD147*T147)</f>
         <v>5</v>
       </c>
       <c r="AO147" s="9">
@@ -50638,7 +50638,7 @@
         <v>504297.80000000005</v>
       </c>
       <c r="AX147" s="31">
-        <f>AD147*AP147</f>
+        <f>IF(E147="cancelled",0,AD147*AP147)</f>
         <v>5</v>
       </c>
       <c r="AY147" s="31">
@@ -50662,7 +50662,7 @@
         <v>504297.80000000005</v>
       </c>
       <c r="BD147" s="31">
-        <f>AD147*AQ147</f>
+        <f>IF(E147="cancelled",0,AD147*AQ147)</f>
         <v>5</v>
       </c>
       <c r="BE147" s="31">
@@ -50686,7 +50686,7 @@
         <v>0</v>
       </c>
       <c r="BJ147" s="31">
-        <f>AD147*AR147</f>
+        <f>IF(E147="cancelled",0,AD147*AR147)</f>
         <v>0</v>
       </c>
       <c r="BK147" s="31">
@@ -50860,7 +50860,7 @@
         <v>0</v>
       </c>
       <c r="AN148" s="9">
-        <f>AD148*T148</f>
+        <f>IF(E148="cancelled",0,AD148*T148)</f>
         <v>5</v>
       </c>
       <c r="AO148" s="9">
@@ -50900,7 +50900,7 @@
         <v>2283233.1100000003</v>
       </c>
       <c r="AX148" s="31">
-        <f>AD148*AP148</f>
+        <f>IF(E148="cancelled",0,AD148*AP148)</f>
         <v>5</v>
       </c>
       <c r="AY148" s="31">
@@ -50924,7 +50924,7 @@
         <v>2283233.1100000003</v>
       </c>
       <c r="BD148" s="31">
-        <f>AD148*AQ148</f>
+        <f>IF(E148="cancelled",0,AD148*AQ148)</f>
         <v>5</v>
       </c>
       <c r="BE148" s="31">
@@ -50948,7 +50948,7 @@
         <v>2283233.1100000003</v>
       </c>
       <c r="BJ148" s="31">
-        <f>AD148*AR148</f>
+        <f>IF(E148="cancelled",0,AD148*AR148)</f>
         <v>5</v>
       </c>
       <c r="BK148" s="31">
@@ -51122,7 +51122,7 @@
         <v>7160415</v>
       </c>
       <c r="AN149" s="9">
-        <f>AD149*T149</f>
+        <f>IF(E149="cancelled",0,AD149*T149)</f>
         <v>5</v>
       </c>
       <c r="AO149" s="9">
@@ -51162,7 +51162,7 @@
         <v>1383261.9500000002</v>
       </c>
       <c r="AX149" s="31">
-        <f>AD149*AP149</f>
+        <f>IF(E149="cancelled",0,AD149*AP149)</f>
         <v>5</v>
       </c>
       <c r="AY149" s="31">
@@ -51186,7 +51186,7 @@
         <v>1383261.9500000002</v>
       </c>
       <c r="BD149" s="31">
-        <f>AD149*AQ149</f>
+        <f>IF(E149="cancelled",0,AD149*AQ149)</f>
         <v>5</v>
       </c>
       <c r="BE149" s="31">
@@ -51210,7 +51210,7 @@
         <v>0</v>
       </c>
       <c r="BJ149" s="31">
-        <f>AD149*AR149</f>
+        <f>IF(E149="cancelled",0,AD149*AR149)</f>
         <v>0</v>
       </c>
       <c r="BK149" s="31">
@@ -51384,7 +51384,7 @@
         <v>0</v>
       </c>
       <c r="AN150" s="9">
-        <f>AD150*T150</f>
+        <f>IF(E150="cancelled",0,AD150*T150)</f>
         <v>7</v>
       </c>
       <c r="AO150" s="9">
@@ -51424,7 +51424,7 @@
         <v>2419968.02</v>
       </c>
       <c r="AX150" s="31">
-        <f>AD150*AP150</f>
+        <f>IF(E150="cancelled",0,AD150*AP150)</f>
         <v>7</v>
       </c>
       <c r="AY150" s="31">
@@ -51448,7 +51448,7 @@
         <v>0</v>
       </c>
       <c r="BD150" s="31">
-        <f>AD150*AQ150</f>
+        <f>IF(E150="cancelled",0,AD150*AQ150)</f>
         <v>0</v>
       </c>
       <c r="BE150" s="31">
@@ -51472,7 +51472,7 @@
         <v>0</v>
       </c>
       <c r="BJ150" s="31">
-        <f>AD150*AR150</f>
+        <f>IF(E150="cancelled",0,AD150*AR150)</f>
         <v>0</v>
       </c>
       <c r="BK150" s="31">
@@ -51646,7 +51646,7 @@
         <v>12211055</v>
       </c>
       <c r="AN151" s="9">
-        <f>AD151*T151</f>
+        <f>IF(E151="cancelled",0,AD151*T151)</f>
         <v>8</v>
       </c>
       <c r="AO151" s="9">
@@ -51686,7 +51686,7 @@
         <v>2501059.5500000003</v>
       </c>
       <c r="AX151" s="31">
-        <f>AD151*AP151</f>
+        <f>IF(E151="cancelled",0,AD151*AP151)</f>
         <v>8</v>
       </c>
       <c r="AY151" s="31">
@@ -51710,7 +51710,7 @@
         <v>2501059.5500000003</v>
       </c>
       <c r="BD151" s="31">
-        <f>AD151*AQ151</f>
+        <f>IF(E151="cancelled",0,AD151*AQ151)</f>
         <v>8</v>
       </c>
       <c r="BE151" s="31">
@@ -51734,7 +51734,7 @@
         <v>0</v>
       </c>
       <c r="BJ151" s="31">
-        <f>AD151*AR151</f>
+        <f>IF(E151="cancelled",0,AD151*AR151)</f>
         <v>0</v>
       </c>
       <c r="BK151" s="31">
@@ -51908,7 +51908,7 @@
         <v>0</v>
       </c>
       <c r="AN152" s="9">
-        <f>AD152*T152</f>
+        <f>IF(E152="cancelled",0,AD152*T152)</f>
         <v>0</v>
       </c>
       <c r="AO152" s="9">
@@ -51948,7 +51948,7 @@
         <v>0</v>
       </c>
       <c r="AX152" s="31">
-        <f>AD152*AP152</f>
+        <f>IF(E152="cancelled",0,AD152*AP152)</f>
         <v>0</v>
       </c>
       <c r="AY152" s="31">
@@ -51972,7 +51972,7 @@
         <v>0</v>
       </c>
       <c r="BD152" s="31">
-        <f>AD152*AQ152</f>
+        <f>IF(E152="cancelled",0,AD152*AQ152)</f>
         <v>0</v>
       </c>
       <c r="BE152" s="31">
@@ -51996,7 +51996,7 @@
         <v>0</v>
       </c>
       <c r="BJ152" s="31">
-        <f>AD152*AR152</f>
+        <f>IF(E152="cancelled",0,AD152*AR152)</f>
         <v>0</v>
       </c>
       <c r="BK152" s="31">
